--- a/GeoApp/GeoData/images/Folder metadata.xlsx
+++ b/GeoApp/GeoData/images/Folder metadata.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE128453-5D05-4E6E-A393-21C8956B084C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAEBCB52-A3E9-43F5-924B-3751E65C5972}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,10 +18,21 @@
   <definedNames>
     <definedName name="ExternalData_1" localSheetId="0" hidden="1">images!$A$1:$C$434</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -36,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1302" uniqueCount="435">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1304" uniqueCount="437">
   <si>
     <t>Name</t>
   </si>
@@ -1341,6 +1352,12 @@
   </si>
   <si>
     <t>Zaytuna Mosque.png</t>
+  </si>
+  <si>
+    <t>Old P</t>
+  </si>
+  <si>
+    <t>New P</t>
   </si>
 </sst>
 </file>
@@ -1376,14 +1393,27 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="5">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
@@ -1408,23 +1438,31 @@
 
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_1" connectionId="1" xr16:uid="{359E6562-D8E6-47C6-B53D-1DA360100208}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
-  <queryTableRefresh nextId="4">
-    <queryTableFields count="3">
+  <queryTableRefresh nextId="6" unboundColumnsRight="2">
+    <queryTableFields count="5">
       <queryTableField id="1" name="Name" tableColumnId="1"/>
       <queryTableField id="2" name="Extension" tableColumnId="2"/>
       <queryTableField id="3" name="Folder Path" tableColumnId="3"/>
+      <queryTableField id="4" dataBound="0" tableColumnId="4"/>
+      <queryTableField id="5" dataBound="0" tableColumnId="5"/>
     </queryTableFields>
   </queryTableRefresh>
 </queryTable>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{493C560A-943A-4F3B-BF8A-D3562ED9BDDE}" name="images" displayName="images" ref="A1:C434" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:C434" xr:uid="{493C560A-943A-4F3B-BF8A-D3562ED9BDDE}"/>
-  <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{97C3AD48-ED15-4240-A2F3-E643CD21217F}" uniqueName="1" name="Name" queryTableFieldId="1" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{CBF1678E-C6A8-485F-87E9-485673F3F1FC}" uniqueName="2" name="Extension" queryTableFieldId="2" dataDxfId="1"/>
-    <tableColumn id="3" xr3:uid="{6B63008C-811B-4083-B469-B25C60F0D166}" uniqueName="3" name="Folder Path" queryTableFieldId="3" dataDxfId="0"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{493C560A-943A-4F3B-BF8A-D3562ED9BDDE}" name="images" displayName="images" ref="A1:E434" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:E434" xr:uid="{493C560A-943A-4F3B-BF8A-D3562ED9BDDE}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{97C3AD48-ED15-4240-A2F3-E643CD21217F}" uniqueName="1" name="Name" queryTableFieldId="1" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{CBF1678E-C6A8-485F-87E9-485673F3F1FC}" uniqueName="2" name="Extension" queryTableFieldId="2" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{6B63008C-811B-4083-B469-B25C60F0D166}" uniqueName="3" name="Folder Path" queryTableFieldId="3" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{FEC723CD-914C-496A-A73A-C414A27A1CCA}" uniqueName="4" name="Old P" queryTableFieldId="4" dataDxfId="0">
+      <calculatedColumnFormula>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{C6347BF8-3EC1-4A04-BACE-990A23AC69CA}" uniqueName="5" name="New P" queryTableFieldId="5" dataDxfId="1">
+      <calculatedColumnFormula>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1693,7 +1731,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F6B3DDA-2410-4DE7-A69C-081638FD86ED}">
-  <dimension ref="A1:C434"/>
+  <sheetPr codeName="Sheet1"/>
+  <dimension ref="A1:E434"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22.109375" bestFit="1" customWidth="1"/>
@@ -1701,7 +1740,7 @@
     <col min="3" max="3" width="52.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1711,8 +1750,14 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D1" t="s">
+        <v>435</v>
+      </c>
+      <c r="E1" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -1722,8 +1767,16 @@
       <c r="C2" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D2" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Abu Dhabi.png</v>
+      </c>
+      <c r="E2" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Abu_Dhabi.png</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -1733,8 +1786,16 @@
       <c r="C3" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D3" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Abuja.png</v>
+      </c>
+      <c r="E3" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Abuja.png</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
@@ -1744,8 +1805,16 @@
       <c r="C4" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D4" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Accra.png</v>
+      </c>
+      <c r="E4" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Accra.png</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
@@ -1755,8 +1824,16 @@
       <c r="C5" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D5" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Addis Ababa.png</v>
+      </c>
+      <c r="E5" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Addis_Ababa.png</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
@@ -1766,8 +1843,16 @@
       <c r="C6" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D6" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Algiers.png</v>
+      </c>
+      <c r="E6" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Algiers.png</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
@@ -1777,8 +1862,16 @@
       <c r="C7" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D7" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Amman.png</v>
+      </c>
+      <c r="E7" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Amman.png</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>11</v>
       </c>
@@ -1788,8 +1881,16 @@
       <c r="C8" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D8" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Amsterdam.png</v>
+      </c>
+      <c r="E8" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Amsterdam.png</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>12</v>
       </c>
@@ -1799,8 +1900,16 @@
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D9" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Andorra.png</v>
+      </c>
+      <c r="E9" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Andorra.png</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>13</v>
       </c>
@@ -1810,8 +1919,16 @@
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D10" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Ankara.png</v>
+      </c>
+      <c r="E10" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Ankara.png</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>14</v>
       </c>
@@ -1821,8 +1938,16 @@
       <c r="C11" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D11" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Antananarivo.png</v>
+      </c>
+      <c r="E11" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Antananarivo.png</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>15</v>
       </c>
@@ -1832,8 +1957,16 @@
       <c r="C12" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D12" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Apia.png</v>
+      </c>
+      <c r="E12" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Apia.png</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>16</v>
       </c>
@@ -1843,8 +1976,16 @@
       <c r="C13" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D13" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Ashgabat.png</v>
+      </c>
+      <c r="E13" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Ashgabat.png</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>17</v>
       </c>
@@ -1854,8 +1995,16 @@
       <c r="C14" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D14" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Asmara.png</v>
+      </c>
+      <c r="E14" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Asmara.png</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>18</v>
       </c>
@@ -1865,8 +2014,16 @@
       <c r="C15" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D15" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Astana.png</v>
+      </c>
+      <c r="E15" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Astana.png</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>19</v>
       </c>
@@ -1876,8 +2033,16 @@
       <c r="C16" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D16" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Asuncion.png</v>
+      </c>
+      <c r="E16" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Asuncion.png</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>20</v>
       </c>
@@ -1887,8 +2052,16 @@
       <c r="C17" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D17" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Athens.png</v>
+      </c>
+      <c r="E17" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Athens.png</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>21</v>
       </c>
@@ -1898,8 +2071,16 @@
       <c r="C18" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D18" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Baghdad.png</v>
+      </c>
+      <c r="E18" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Baghdad.png</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>22</v>
       </c>
@@ -1909,8 +2090,16 @@
       <c r="C19" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D19" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Baku.png</v>
+      </c>
+      <c r="E19" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Baku.png</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>23</v>
       </c>
@@ -1920,8 +2109,16 @@
       <c r="C20" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D20" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Bamako.png</v>
+      </c>
+      <c r="E20" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Bamako.png</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>24</v>
       </c>
@@ -1931,8 +2128,16 @@
       <c r="C21" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D21" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Bandar Seri.png</v>
+      </c>
+      <c r="E21" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Bandar_Seri.png</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>25</v>
       </c>
@@ -1942,8 +2147,16 @@
       <c r="C22" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D22" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Bangkok.png</v>
+      </c>
+      <c r="E22" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Bangkok.png</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>26</v>
       </c>
@@ -1953,8 +2166,16 @@
       <c r="C23" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D23" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Bangui.png</v>
+      </c>
+      <c r="E23" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Bangui.png</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>27</v>
       </c>
@@ -1964,8 +2185,16 @@
       <c r="C24" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D24" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Banjul.png</v>
+      </c>
+      <c r="E24" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Banjul.png</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>28</v>
       </c>
@@ -1975,8 +2204,16 @@
       <c r="C25" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D25" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Basseterre.png</v>
+      </c>
+      <c r="E25" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Basseterre.png</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>29</v>
       </c>
@@ -1986,8 +2223,16 @@
       <c r="C26" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D26" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Beijing.png</v>
+      </c>
+      <c r="E26" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Beijing.png</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>30</v>
       </c>
@@ -1997,8 +2242,16 @@
       <c r="C27" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D27" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Beirut.png</v>
+      </c>
+      <c r="E27" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Beirut.png</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>31</v>
       </c>
@@ -2008,8 +2261,16 @@
       <c r="C28" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D28" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Belgrade.png</v>
+      </c>
+      <c r="E28" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Belgrade.png</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>32</v>
       </c>
@@ -2019,8 +2280,16 @@
       <c r="C29" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D29" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Berlin.png</v>
+      </c>
+      <c r="E29" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Berlin.png</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>33</v>
       </c>
@@ -2030,8 +2299,16 @@
       <c r="C30" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D30" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Bern.png</v>
+      </c>
+      <c r="E30" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Bern.png</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>34</v>
       </c>
@@ -2041,8 +2318,16 @@
       <c r="C31" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D31" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Bishkek.png</v>
+      </c>
+      <c r="E31" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Bishkek.png</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>35</v>
       </c>
@@ -2052,8 +2337,16 @@
       <c r="C32" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D32" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Bissau.png</v>
+      </c>
+      <c r="E32" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Bissau.png</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>36</v>
       </c>
@@ -2063,8 +2356,16 @@
       <c r="C33" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D33" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Bogota.png</v>
+      </c>
+      <c r="E33" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Bogota.png</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>37</v>
       </c>
@@ -2074,8 +2375,16 @@
       <c r="C34" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D34" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Brasilia.png</v>
+      </c>
+      <c r="E34" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Brasilia.png</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>38</v>
       </c>
@@ -2085,8 +2394,16 @@
       <c r="C35" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D35" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Bratislava.png</v>
+      </c>
+      <c r="E35" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Bratislava.png</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>39</v>
       </c>
@@ -2096,8 +2413,16 @@
       <c r="C36" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D36" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Brazzaville.png</v>
+      </c>
+      <c r="E36" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Brazzaville.png</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>40</v>
       </c>
@@ -2107,8 +2432,16 @@
       <c r="C37" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D37" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Bridgetown.png</v>
+      </c>
+      <c r="E37" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Bridgetown.png</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
         <v>41</v>
       </c>
@@ -2118,8 +2451,16 @@
       <c r="C38" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D38" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Brussels.png</v>
+      </c>
+      <c r="E38" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Brussels.png</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
         <v>42</v>
       </c>
@@ -2129,8 +2470,16 @@
       <c r="C39" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D39" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Bucharest.png</v>
+      </c>
+      <c r="E39" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Bucharest.png</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>43</v>
       </c>
@@ -2140,8 +2489,16 @@
       <c r="C40" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D40" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Budapest.png</v>
+      </c>
+      <c r="E40" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Budapest.png</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>44</v>
       </c>
@@ -2151,8 +2508,16 @@
       <c r="C41" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D41" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Buenos Aires.png</v>
+      </c>
+      <c r="E41" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Buenos_Aires.png</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>45</v>
       </c>
@@ -2162,8 +2527,16 @@
       <c r="C42" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D42" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Cairo.png</v>
+      </c>
+      <c r="E42" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Cairo.png</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
         <v>46</v>
       </c>
@@ -2173,8 +2546,16 @@
       <c r="C43" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D43" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Canberra.png</v>
+      </c>
+      <c r="E43" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Canberra.png</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
         <v>47</v>
       </c>
@@ -2184,8 +2565,16 @@
       <c r="C44" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D44" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Caracas.png</v>
+      </c>
+      <c r="E44" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Caracas.png</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
         <v>48</v>
       </c>
@@ -2195,8 +2584,16 @@
       <c r="C45" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D45" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Castries.png</v>
+      </c>
+      <c r="E45" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Castries.png</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
         <v>49</v>
       </c>
@@ -2206,8 +2603,16 @@
       <c r="C46" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D46" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Chisinau.png</v>
+      </c>
+      <c r="E46" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Chisinau.png</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
         <v>50</v>
       </c>
@@ -2217,8 +2622,16 @@
       <c r="C47" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D47" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Colombo.png</v>
+      </c>
+      <c r="E47" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Colombo.png</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
         <v>51</v>
       </c>
@@ -2228,8 +2641,16 @@
       <c r="C48" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D48" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Conakry.png</v>
+      </c>
+      <c r="E48" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Conakry.png</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
         <v>52</v>
       </c>
@@ -2239,8 +2660,16 @@
       <c r="C49" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D49" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Copenhagen.png</v>
+      </c>
+      <c r="E49" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Copenhagen.png</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
         <v>53</v>
       </c>
@@ -2250,8 +2679,16 @@
       <c r="C50" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D50" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Dakar.png</v>
+      </c>
+      <c r="E50" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Dakar.png</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
         <v>54</v>
       </c>
@@ -2261,8 +2698,16 @@
       <c r="C51" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D51" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Damascus.png</v>
+      </c>
+      <c r="E51" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Damascus.png</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
         <v>55</v>
       </c>
@@ -2272,8 +2717,16 @@
       <c r="C52" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D52" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Dhaka.png</v>
+      </c>
+      <c r="E52" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Dhaka.png</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
         <v>56</v>
       </c>
@@ -2283,8 +2736,16 @@
       <c r="C53" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D53" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Dili.png</v>
+      </c>
+      <c r="E53" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Dili.png</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
         <v>57</v>
       </c>
@@ -2294,8 +2755,16 @@
       <c r="C54" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D54" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Dodoma.png</v>
+      </c>
+      <c r="E54" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Dodoma.png</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
         <v>58</v>
       </c>
@@ -2305,8 +2774,16 @@
       <c r="C55" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D55" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Doha.png</v>
+      </c>
+      <c r="E55" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Doha.png</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
         <v>59</v>
       </c>
@@ -2316,8 +2793,16 @@
       <c r="C56" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D56" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Dublin.png</v>
+      </c>
+      <c r="E56" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Dublin.png</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
         <v>60</v>
       </c>
@@ -2327,8 +2812,16 @@
       <c r="C57" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D57" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Dushanbe.png</v>
+      </c>
+      <c r="E57" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Dushanbe.png</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
         <v>61</v>
       </c>
@@ -2338,8 +2831,16 @@
       <c r="C58" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D58" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Freetown.png</v>
+      </c>
+      <c r="E58" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Freetown.png</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
         <v>62</v>
       </c>
@@ -2349,8 +2850,16 @@
       <c r="C59" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D59" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Gaborone.png</v>
+      </c>
+      <c r="E59" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Gaborone.png</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
         <v>63</v>
       </c>
@@ -2360,8 +2869,16 @@
       <c r="C60" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D60" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Guatemala.png</v>
+      </c>
+      <c r="E60" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Guatemala.png</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
         <v>64</v>
       </c>
@@ -2371,8 +2888,16 @@
       <c r="C61" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D61" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Hanoi.png</v>
+      </c>
+      <c r="E61" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Hanoi.png</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
         <v>65</v>
       </c>
@@ -2382,8 +2907,16 @@
       <c r="C62" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D62" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Harare.png</v>
+      </c>
+      <c r="E62" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Harare.png</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
         <v>66</v>
       </c>
@@ -2393,8 +2926,16 @@
       <c r="C63" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D63" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Havana.png</v>
+      </c>
+      <c r="E63" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Havana.png</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
         <v>67</v>
       </c>
@@ -2404,8 +2945,16 @@
       <c r="C64" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D64" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Helsinki.png</v>
+      </c>
+      <c r="E64" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Helsinki.png</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
         <v>68</v>
       </c>
@@ -2415,8 +2964,16 @@
       <c r="C65" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D65" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Islamabad.png</v>
+      </c>
+      <c r="E65" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Islamabad.png</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
         <v>69</v>
       </c>
@@ -2426,8 +2983,16 @@
       <c r="C66" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D66" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Jakarta.png</v>
+      </c>
+      <c r="E66" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Jakarta.png</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
         <v>70</v>
       </c>
@@ -2437,8 +3002,16 @@
       <c r="C67" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D67" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Jerusalem.png</v>
+      </c>
+      <c r="E67" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Jerusalem.png</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
         <v>71</v>
       </c>
@@ -2448,8 +3021,16 @@
       <c r="C68" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D68" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Kabul.png</v>
+      </c>
+      <c r="E68" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Kabul.png</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
         <v>72</v>
       </c>
@@ -2459,8 +3040,16 @@
       <c r="C69" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D69" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Kampala.png</v>
+      </c>
+      <c r="E69" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Kampala.png</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
         <v>73</v>
       </c>
@@ -2470,8 +3059,16 @@
       <c r="C70" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D70" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Kathmandu.png</v>
+      </c>
+      <c r="E70" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Kathmandu.png</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
         <v>74</v>
       </c>
@@ -2481,8 +3078,16 @@
       <c r="C71" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D71" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Khartoum.png</v>
+      </c>
+      <c r="E71" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Khartoum.png</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
         <v>75</v>
       </c>
@@ -2492,8 +3097,16 @@
       <c r="C72" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D72" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Kigali.png</v>
+      </c>
+      <c r="E72" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Kigali.png</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
         <v>76</v>
       </c>
@@ -2503,8 +3116,16 @@
       <c r="C73" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D73" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Kingston.png</v>
+      </c>
+      <c r="E73" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Kingston.png</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
         <v>77</v>
       </c>
@@ -2514,8 +3135,16 @@
       <c r="C74" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D74" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Kinshasa.png</v>
+      </c>
+      <c r="E74" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Kinshasa.png</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
         <v>78</v>
       </c>
@@ -2525,8 +3154,16 @@
       <c r="C75" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D75" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Kuala Lumpur.png</v>
+      </c>
+      <c r="E75" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Kuala_Lumpur.png</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
         <v>79</v>
       </c>
@@ -2536,8 +3173,16 @@
       <c r="C76" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D76" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Kuwait.png</v>
+      </c>
+      <c r="E76" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Kuwait.png</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
         <v>80</v>
       </c>
@@ -2547,8 +3192,16 @@
       <c r="C77" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D77" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Kyiv.png</v>
+      </c>
+      <c r="E77" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Kyiv.png</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
         <v>81</v>
       </c>
@@ -2558,8 +3211,16 @@
       <c r="C78" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D78" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Libreville.png</v>
+      </c>
+      <c r="E78" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Libreville.png</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
         <v>82</v>
       </c>
@@ -2569,8 +3230,16 @@
       <c r="C79" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D79" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Lilongwe.png</v>
+      </c>
+      <c r="E79" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Lilongwe.png</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
         <v>83</v>
       </c>
@@ -2580,8 +3249,16 @@
       <c r="C80" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D80" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Lima.png</v>
+      </c>
+      <c r="E80" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Lima.png</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
         <v>84</v>
       </c>
@@ -2591,8 +3268,16 @@
       <c r="C81" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D81" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Lisbon.png</v>
+      </c>
+      <c r="E81" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Lisbon.png</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
         <v>85</v>
       </c>
@@ -2602,8 +3287,16 @@
       <c r="C82" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D82" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Ljubljana.png</v>
+      </c>
+      <c r="E82" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Ljubljana.png</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
         <v>86</v>
       </c>
@@ -2613,8 +3306,16 @@
       <c r="C83" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D83" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Lome.png</v>
+      </c>
+      <c r="E83" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Lome.png</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
         <v>87</v>
       </c>
@@ -2624,8 +3325,16 @@
       <c r="C84" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D84" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\London.png</v>
+      </c>
+      <c r="E84" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\London.png</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
         <v>88</v>
       </c>
@@ -2635,8 +3344,16 @@
       <c r="C85" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D85" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Luanda.png</v>
+      </c>
+      <c r="E85" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Luanda.png</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
         <v>89</v>
       </c>
@@ -2646,8 +3363,16 @@
       <c r="C86" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D86" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Lusaka.png</v>
+      </c>
+      <c r="E86" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Lusaka.png</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
         <v>90</v>
       </c>
@@ -2657,8 +3382,16 @@
       <c r="C87" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D87" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Luxembourg.png</v>
+      </c>
+      <c r="E87" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Luxembourg.png</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
         <v>91</v>
       </c>
@@ -2668,8 +3401,16 @@
       <c r="C88" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D88" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Madrid.png</v>
+      </c>
+      <c r="E88" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Madrid.png</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
         <v>92</v>
       </c>
@@ -2679,8 +3420,16 @@
       <c r="C89" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D89" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Malabo.png</v>
+      </c>
+      <c r="E89" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Malabo.png</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
         <v>93</v>
       </c>
@@ -2690,8 +3439,16 @@
       <c r="C90" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D90" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Male.png</v>
+      </c>
+      <c r="E90" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Male.png</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
         <v>94</v>
       </c>
@@ -2701,8 +3458,16 @@
       <c r="C91" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D91" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Managua.png</v>
+      </c>
+      <c r="E91" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Managua.png</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
         <v>95</v>
       </c>
@@ -2712,8 +3477,16 @@
       <c r="C92" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D92" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Manama.png</v>
+      </c>
+      <c r="E92" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Manama.png</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
         <v>96</v>
       </c>
@@ -2723,8 +3496,16 @@
       <c r="C93" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D93" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Manila.png</v>
+      </c>
+      <c r="E93" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Manila.png</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
         <v>97</v>
       </c>
@@ -2734,8 +3515,16 @@
       <c r="C94" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D94" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Maputo.png</v>
+      </c>
+      <c r="E94" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Maputo.png</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
         <v>98</v>
       </c>
@@ -2745,8 +3534,16 @@
       <c r="C95" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D95" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Maseru.png</v>
+      </c>
+      <c r="E95" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Maseru.png</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
         <v>99</v>
       </c>
@@ -2756,8 +3553,16 @@
       <c r="C96" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D96" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Mexico City.png</v>
+      </c>
+      <c r="E96" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Mexico_City.png</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
         <v>100</v>
       </c>
@@ -2767,8 +3572,16 @@
       <c r="C97" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D97" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Minsk.png</v>
+      </c>
+      <c r="E97" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Minsk.png</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
         <v>101</v>
       </c>
@@ -2778,8 +3591,16 @@
       <c r="C98" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D98" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Mogadishu.png</v>
+      </c>
+      <c r="E98" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Mogadishu.png</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A99" s="1" t="s">
         <v>102</v>
       </c>
@@ -2789,8 +3610,16 @@
       <c r="C99" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D99" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Monaco.png</v>
+      </c>
+      <c r="E99" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Monaco.png</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
         <v>103</v>
       </c>
@@ -2800,8 +3629,16 @@
       <c r="C100" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D100" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Monrovia.png</v>
+      </c>
+      <c r="E100" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Monrovia.png</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
         <v>104</v>
       </c>
@@ -2811,8 +3648,16 @@
       <c r="C101" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D101" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Montevideo.png</v>
+      </c>
+      <c r="E101" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Montevideo.png</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
         <v>105</v>
       </c>
@@ -2822,8 +3667,16 @@
       <c r="C102" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D102" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Moroni.png</v>
+      </c>
+      <c r="E102" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Moroni.png</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
         <v>106</v>
       </c>
@@ -2833,8 +3686,16 @@
       <c r="C103" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D103" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Moscow.png</v>
+      </c>
+      <c r="E103" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Moscow.png</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="s">
         <v>107</v>
       </c>
@@ -2844,8 +3705,16 @@
       <c r="C104" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D104" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Muscat.png</v>
+      </c>
+      <c r="E104" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Muscat.png</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
         <v>108</v>
       </c>
@@ -2855,8 +3724,16 @@
       <c r="C105" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D105" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Nairobi.png</v>
+      </c>
+      <c r="E105" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Nairobi.png</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A106" s="1" t="s">
         <v>109</v>
       </c>
@@ -2866,8 +3743,16 @@
       <c r="C106" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D106" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Nassau.png</v>
+      </c>
+      <c r="E106" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Nassau.png</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A107" s="1" t="s">
         <v>110</v>
       </c>
@@ -2877,8 +3762,16 @@
       <c r="C107" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D107" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Naypyidaw.png</v>
+      </c>
+      <c r="E107" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Naypyidaw.png</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
         <v>111</v>
       </c>
@@ -2888,8 +3781,16 @@
       <c r="C108" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D108" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Ndjamena.png</v>
+      </c>
+      <c r="E108" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Ndjamena.png</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A109" s="1" t="s">
         <v>112</v>
       </c>
@@ -2899,8 +3800,16 @@
       <c r="C109" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D109" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\New Delhi.png</v>
+      </c>
+      <c r="E109" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\New_Delhi.png</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A110" s="1" t="s">
         <v>113</v>
       </c>
@@ -2910,8 +3819,16 @@
       <c r="C110" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D110" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Niamey.png</v>
+      </c>
+      <c r="E110" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Niamey.png</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A111" s="1" t="s">
         <v>114</v>
       </c>
@@ -2921,8 +3838,16 @@
       <c r="C111" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D111" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Nicosia.png</v>
+      </c>
+      <c r="E111" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Nicosia.png</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="s">
         <v>115</v>
       </c>
@@ -2932,8 +3857,16 @@
       <c r="C112" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D112" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Nouakchott.png</v>
+      </c>
+      <c r="E112" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Nouakchott.png</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A113" s="1" t="s">
         <v>116</v>
       </c>
@@ -2943,8 +3876,16 @@
       <c r="C113" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D113" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Oslo.png</v>
+      </c>
+      <c r="E113" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Oslo.png</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
         <v>117</v>
       </c>
@@ -2954,8 +3895,16 @@
       <c r="C114" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D114" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Ottawa.png</v>
+      </c>
+      <c r="E114" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Ottawa.png</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A115" s="1" t="s">
         <v>118</v>
       </c>
@@ -2965,8 +3914,16 @@
       <c r="C115" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D115" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Ouagadougou.png</v>
+      </c>
+      <c r="E115" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Ouagadougou.png</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A116" s="1" t="s">
         <v>119</v>
       </c>
@@ -2976,8 +3933,16 @@
       <c r="C116" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D116" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Panama City.png</v>
+      </c>
+      <c r="E116" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Panama_City.png</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A117" s="1" t="s">
         <v>120</v>
       </c>
@@ -2987,8 +3952,16 @@
       <c r="C117" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D117" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Paramaribo.png</v>
+      </c>
+      <c r="E117" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Paramaribo.png</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A118" s="1" t="s">
         <v>121</v>
       </c>
@@ -2998,8 +3971,16 @@
       <c r="C118" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D118" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Paris.png</v>
+      </c>
+      <c r="E118" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Paris.png</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A119" s="1" t="s">
         <v>122</v>
       </c>
@@ -3009,8 +3990,16 @@
       <c r="C119" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D119" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Phnom Penh.png</v>
+      </c>
+      <c r="E119" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Phnom_Penh.png</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A120" s="1" t="s">
         <v>123</v>
       </c>
@@ -3020,8 +4009,16 @@
       <c r="C120" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D120" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Podgorica.png</v>
+      </c>
+      <c r="E120" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Podgorica.png</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A121" s="1" t="s">
         <v>124</v>
       </c>
@@ -3031,8 +4028,16 @@
       <c r="C121" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D121" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Port au Prince.png</v>
+      </c>
+      <c r="E121" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Port_au_Prince.png</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A122" s="1" t="s">
         <v>125</v>
       </c>
@@ -3042,8 +4047,16 @@
       <c r="C122" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D122" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Port Louis.png</v>
+      </c>
+      <c r="E122" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Port_Louis.png</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A123" s="1" t="s">
         <v>126</v>
       </c>
@@ -3053,8 +4066,16 @@
       <c r="C123" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D123" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Port of Spain.png</v>
+      </c>
+      <c r="E123" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Port_of_Spain.png</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A124" s="1" t="s">
         <v>127</v>
       </c>
@@ -3064,8 +4085,16 @@
       <c r="C124" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D124" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Porto Novo.png</v>
+      </c>
+      <c r="E124" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Porto_Novo.png</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A125" s="1" t="s">
         <v>128</v>
       </c>
@@ -3075,8 +4104,16 @@
       <c r="C125" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D125" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Prague.png</v>
+      </c>
+      <c r="E125" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Prague.png</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A126" s="1" t="s">
         <v>129</v>
       </c>
@@ -3086,8 +4123,16 @@
       <c r="C126" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D126" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Praia.png</v>
+      </c>
+      <c r="E126" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Praia.png</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A127" s="1" t="s">
         <v>130</v>
       </c>
@@ -3097,8 +4142,16 @@
       <c r="C127" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D127" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Pretoria.png</v>
+      </c>
+      <c r="E127" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Pretoria.png</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A128" s="1" t="s">
         <v>131</v>
       </c>
@@ -3108,8 +4161,16 @@
       <c r="C128" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D128" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Pyongyang.png</v>
+      </c>
+      <c r="E128" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Pyongyang.png</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A129" s="1" t="s">
         <v>132</v>
       </c>
@@ -3119,8 +4180,16 @@
       <c r="C129" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D129" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Quito.png</v>
+      </c>
+      <c r="E129" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Quito.png</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A130" s="1" t="s">
         <v>133</v>
       </c>
@@ -3130,8 +4199,16 @@
       <c r="C130" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D130" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Rabat.png</v>
+      </c>
+      <c r="E130" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Rabat.png</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A131" s="1" t="s">
         <v>134</v>
       </c>
@@ -3141,8 +4218,16 @@
       <c r="C131" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D131" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Reykjavik.png</v>
+      </c>
+      <c r="E131" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Reykjavik.png</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A132" s="1" t="s">
         <v>135</v>
       </c>
@@ -3152,8 +4237,16 @@
       <c r="C132" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D132" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Riga.png</v>
+      </c>
+      <c r="E132" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Riga.png</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A133" s="1" t="s">
         <v>136</v>
       </c>
@@ -3163,8 +4256,16 @@
       <c r="C133" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D133" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Riyadh.png</v>
+      </c>
+      <c r="E133" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Riyadh.png</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A134" s="1" t="s">
         <v>137</v>
       </c>
@@ -3174,8 +4275,16 @@
       <c r="C134" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D134" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Rome.png</v>
+      </c>
+      <c r="E134" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Rome.png</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A135" s="1" t="s">
         <v>138</v>
       </c>
@@ -3185,8 +4294,16 @@
       <c r="C135" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D135" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\San Jose.png</v>
+      </c>
+      <c r="E135" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\San_Jose.png</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A136" s="1" t="s">
         <v>139</v>
       </c>
@@ -3196,8 +4313,16 @@
       <c r="C136" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D136" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\San Salvador.png</v>
+      </c>
+      <c r="E136" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\San_Salvador.png</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A137" s="1" t="s">
         <v>140</v>
       </c>
@@ -3207,8 +4332,16 @@
       <c r="C137" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D137" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Sanaa.png</v>
+      </c>
+      <c r="E137" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Sanaa.png</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A138" s="1" t="s">
         <v>141</v>
       </c>
@@ -3218,8 +4351,16 @@
       <c r="C138" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D138" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Santiago.png</v>
+      </c>
+      <c r="E138" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Santiago.png</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A139" s="1" t="s">
         <v>142</v>
       </c>
@@ -3229,8 +4370,16 @@
       <c r="C139" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D139" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Santo Domingo.png</v>
+      </c>
+      <c r="E139" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Santo_Domingo.png</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A140" s="1" t="s">
         <v>143</v>
       </c>
@@ -3240,8 +4389,16 @@
       <c r="C140" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D140" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Sarajevo.png</v>
+      </c>
+      <c r="E140" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Sarajevo.png</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A141" s="1" t="s">
         <v>144</v>
       </c>
@@ -3251,8 +4408,16 @@
       <c r="C141" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D141" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Seoul.png</v>
+      </c>
+      <c r="E141" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Seoul.png</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A142" s="1" t="s">
         <v>145</v>
       </c>
@@ -3262,8 +4427,16 @@
       <c r="C142" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D142" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Singapore.png</v>
+      </c>
+      <c r="E142" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Singapore.png</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A143" s="1" t="s">
         <v>146</v>
       </c>
@@ -3273,8 +4446,16 @@
       <c r="C143" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D143" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Skopje.png</v>
+      </c>
+      <c r="E143" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Skopje.png</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A144" s="1" t="s">
         <v>147</v>
       </c>
@@ -3284,8 +4465,16 @@
       <c r="C144" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D144" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Sofia.png</v>
+      </c>
+      <c r="E144" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Sofia.png</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A145" s="1" t="s">
         <v>148</v>
       </c>
@@ -3295,8 +4484,16 @@
       <c r="C145" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D145" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Stockholm.png</v>
+      </c>
+      <c r="E145" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Stockholm.png</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A146" s="1" t="s">
         <v>149</v>
       </c>
@@ -3306,8 +4503,16 @@
       <c r="C146" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D146" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Sucre.png</v>
+      </c>
+      <c r="E146" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Sucre.png</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A147" s="1" t="s">
         <v>150</v>
       </c>
@@ -3317,8 +4522,16 @@
       <c r="C147" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D147" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Tallinn.png</v>
+      </c>
+      <c r="E147" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Tallinn.png</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A148" s="1" t="s">
         <v>151</v>
       </c>
@@ -3328,8 +4541,16 @@
       <c r="C148" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D148" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Tashkent.png</v>
+      </c>
+      <c r="E148" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Tashkent.png</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A149" s="1" t="s">
         <v>152</v>
       </c>
@@ -3339,8 +4560,16 @@
       <c r="C149" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D149" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Tbilisi.png</v>
+      </c>
+      <c r="E149" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Tbilisi.png</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A150" s="1" t="s">
         <v>153</v>
       </c>
@@ -3350,8 +4579,16 @@
       <c r="C150" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D150" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Tegucigalpa.png</v>
+      </c>
+      <c r="E150" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Tegucigalpa.png</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A151" s="1" t="s">
         <v>154</v>
       </c>
@@ -3361,8 +4598,16 @@
       <c r="C151" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D151" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Tehran.png</v>
+      </c>
+      <c r="E151" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Tehran.png</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A152" s="1" t="s">
         <v>155</v>
       </c>
@@ -3372,8 +4617,16 @@
       <c r="C152" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D152" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Tirana.png</v>
+      </c>
+      <c r="E152" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Tirana.png</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A153" s="1" t="s">
         <v>156</v>
       </c>
@@ -3383,8 +4636,16 @@
       <c r="C153" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D153" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Tokyo.png</v>
+      </c>
+      <c r="E153" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Tokyo.png</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A154" s="1" t="s">
         <v>157</v>
       </c>
@@ -3394,8 +4655,16 @@
       <c r="C154" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D154" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Tripoli.png</v>
+      </c>
+      <c r="E154" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Tripoli.png</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A155" s="1" t="s">
         <v>158</v>
       </c>
@@ -3405,8 +4674,16 @@
       <c r="C155" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D155" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Tunis.png</v>
+      </c>
+      <c r="E155" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Tunis.png</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A156" s="1" t="s">
         <v>159</v>
       </c>
@@ -3416,8 +4693,16 @@
       <c r="C156" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D156" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Ulaanbaatar.png</v>
+      </c>
+      <c r="E156" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Ulaanbaatar.png</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A157" s="1" t="s">
         <v>160</v>
       </c>
@@ -3427,8 +4712,16 @@
       <c r="C157" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D157" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Vaduz.png</v>
+      </c>
+      <c r="E157" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Vaduz.png</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A158" s="1" t="s">
         <v>161</v>
       </c>
@@ -3438,8 +4731,16 @@
       <c r="C158" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D158" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Valletta.png</v>
+      </c>
+      <c r="E158" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Valletta.png</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A159" s="1" t="s">
         <v>162</v>
       </c>
@@ -3449,8 +4750,16 @@
       <c r="C159" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D159" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Vatican.png</v>
+      </c>
+      <c r="E159" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Vatican.png</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A160" s="1" t="s">
         <v>163</v>
       </c>
@@ -3460,8 +4769,16 @@
       <c r="C160" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D160" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Victoria.png</v>
+      </c>
+      <c r="E160" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Victoria.png</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A161" s="1" t="s">
         <v>164</v>
       </c>
@@ -3471,8 +4788,16 @@
       <c r="C161" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D161" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Vienna.png</v>
+      </c>
+      <c r="E161" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Vienna.png</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A162" s="1" t="s">
         <v>165</v>
       </c>
@@ -3482,8 +4807,16 @@
       <c r="C162" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D162" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Vientiane.png</v>
+      </c>
+      <c r="E162" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Vientiane.png</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A163" s="1" t="s">
         <v>166</v>
       </c>
@@ -3493,8 +4826,16 @@
       <c r="C163" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D163" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Vilnius.png</v>
+      </c>
+      <c r="E163" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Vilnius.png</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A164" s="1" t="s">
         <v>167</v>
       </c>
@@ -3504,8 +4845,16 @@
       <c r="C164" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D164" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Warsaw.png</v>
+      </c>
+      <c r="E164" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Warsaw.png</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A165" s="1" t="s">
         <v>168</v>
       </c>
@@ -3515,8 +4864,16 @@
       <c r="C165" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D165" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Washington.png</v>
+      </c>
+      <c r="E165" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Washington.png</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A166" s="1" t="s">
         <v>169</v>
       </c>
@@ -3526,8 +4883,16 @@
       <c r="C166" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D166" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Wellington.png</v>
+      </c>
+      <c r="E166" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Wellington.png</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A167" s="1" t="s">
         <v>170</v>
       </c>
@@ -3537,8 +4902,16 @@
       <c r="C167" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D167" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Windhoek.png</v>
+      </c>
+      <c r="E167" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Windhoek.png</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A168" s="1" t="s">
         <v>171</v>
       </c>
@@ -3548,8 +4921,16 @@
       <c r="C168" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D168" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Yamoussoukro.png</v>
+      </c>
+      <c r="E168" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Yamoussoukro.png</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A169" s="1" t="s">
         <v>172</v>
       </c>
@@ -3559,8 +4940,16 @@
       <c r="C169" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D169" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Yaounde.png</v>
+      </c>
+      <c r="E169" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Yaounde.png</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A170" s="1" t="s">
         <v>173</v>
       </c>
@@ -3570,8 +4959,16 @@
       <c r="C170" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D170" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Yerevan.png</v>
+      </c>
+      <c r="E170" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Yerevan.png</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A171" s="1" t="s">
         <v>174</v>
       </c>
@@ -3581,8 +4978,16 @@
       <c r="C171" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D171" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Zagreb.png</v>
+      </c>
+      <c r="E171" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\capitals\Zagreb.png</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A172" s="1" t="s">
         <v>175</v>
       </c>
@@ -3592,8 +4997,16 @@
       <c r="C172" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D172" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Afghanistan.png</v>
+      </c>
+      <c r="E172" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Afghanistan.png</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A173" s="1" t="s">
         <v>177</v>
       </c>
@@ -3603,8 +5016,16 @@
       <c r="C173" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D173" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Albania.png</v>
+      </c>
+      <c r="E173" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Albania.png</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A174" s="1" t="s">
         <v>178</v>
       </c>
@@ -3614,8 +5035,16 @@
       <c r="C174" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D174" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Algeria.png</v>
+      </c>
+      <c r="E174" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Algeria.png</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A175" s="1" t="s">
         <v>12</v>
       </c>
@@ -3625,8 +5054,16 @@
       <c r="C175" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D175" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Andorra.png</v>
+      </c>
+      <c r="E175" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Andorra.png</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A176" s="1" t="s">
         <v>179</v>
       </c>
@@ -3636,8 +5073,16 @@
       <c r="C176" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D176" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Angola.png</v>
+      </c>
+      <c r="E176" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Angola.png</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A177" s="1" t="s">
         <v>180</v>
       </c>
@@ -3647,8 +5092,16 @@
       <c r="C177" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D177" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Arab Emirates.png</v>
+      </c>
+      <c r="E177" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Arab_Emirates.png</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A178" s="1" t="s">
         <v>181</v>
       </c>
@@ -3658,8 +5111,16 @@
       <c r="C178" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D178" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Argentina.png</v>
+      </c>
+      <c r="E178" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Argentina.png</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A179" s="1" t="s">
         <v>182</v>
       </c>
@@ -3669,8 +5130,16 @@
       <c r="C179" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D179" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Armenia.png</v>
+      </c>
+      <c r="E179" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Armenia.png</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A180" s="1" t="s">
         <v>183</v>
       </c>
@@ -3680,8 +5149,16 @@
       <c r="C180" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D180" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Australia.png</v>
+      </c>
+      <c r="E180" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Australia.png</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A181" s="1" t="s">
         <v>184</v>
       </c>
@@ -3691,8 +5168,16 @@
       <c r="C181" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D181" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Austria.png</v>
+      </c>
+      <c r="E181" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Austria.png</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A182" s="1" t="s">
         <v>185</v>
       </c>
@@ -3702,8 +5187,16 @@
       <c r="C182" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D182" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Azerbaijan.png</v>
+      </c>
+      <c r="E182" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Azerbaijan.png</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A183" s="1" t="s">
         <v>186</v>
       </c>
@@ -3713,8 +5206,16 @@
       <c r="C183" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D183" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Bahamas.png</v>
+      </c>
+      <c r="E183" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Bahamas.png</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A184" s="1" t="s">
         <v>187</v>
       </c>
@@ -3724,8 +5225,16 @@
       <c r="C184" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D184" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Bahrain.png</v>
+      </c>
+      <c r="E184" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Bahrain.png</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A185" s="1" t="s">
         <v>188</v>
       </c>
@@ -3735,8 +5244,16 @@
       <c r="C185" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D185" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Bangladesh.png</v>
+      </c>
+      <c r="E185" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Bangladesh.png</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A186" s="1" t="s">
         <v>189</v>
       </c>
@@ -3746,8 +5263,16 @@
       <c r="C186" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D186" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Barbados.png</v>
+      </c>
+      <c r="E186" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Barbados.png</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A187" s="1" t="s">
         <v>190</v>
       </c>
@@ -3757,8 +5282,16 @@
       <c r="C187" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D187" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Belarus.png</v>
+      </c>
+      <c r="E187" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Belarus.png</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A188" s="1" t="s">
         <v>191</v>
       </c>
@@ -3768,8 +5301,16 @@
       <c r="C188" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D188" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Belgium.png</v>
+      </c>
+      <c r="E188" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Belgium.png</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A189" s="1" t="s">
         <v>192</v>
       </c>
@@ -3779,8 +5320,16 @@
       <c r="C189" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D189" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Belize.png</v>
+      </c>
+      <c r="E189" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Belize.png</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A190" s="1" t="s">
         <v>193</v>
       </c>
@@ -3790,8 +5339,16 @@
       <c r="C190" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D190" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Benin.png</v>
+      </c>
+      <c r="E190" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Benin.png</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A191" s="1" t="s">
         <v>194</v>
       </c>
@@ -3801,8 +5358,16 @@
       <c r="C191" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D191" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Bhutan.png</v>
+      </c>
+      <c r="E191" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Bhutan.png</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A192" s="1" t="s">
         <v>195</v>
       </c>
@@ -3812,8 +5377,16 @@
       <c r="C192" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D192" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Bolivia.png</v>
+      </c>
+      <c r="E192" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Bolivia.png</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A193" s="1" t="s">
         <v>196</v>
       </c>
@@ -3823,8 +5396,16 @@
       <c r="C193" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D193" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Bosnia.png</v>
+      </c>
+      <c r="E193" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Bosnia.png</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A194" s="1" t="s">
         <v>197</v>
       </c>
@@ -3834,8 +5415,16 @@
       <c r="C194" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D194" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Botswana.png</v>
+      </c>
+      <c r="E194" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Botswana.png</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A195" s="1" t="s">
         <v>198</v>
       </c>
@@ -3845,8 +5434,16 @@
       <c r="C195" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D195" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Brazil.png</v>
+      </c>
+      <c r="E195" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Brazil.png</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A196" s="1" t="s">
         <v>199</v>
       </c>
@@ -3856,8 +5453,16 @@
       <c r="C196" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D196" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Brunei.png</v>
+      </c>
+      <c r="E196" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Brunei.png</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A197" s="1" t="s">
         <v>200</v>
       </c>
@@ -3867,8 +5472,16 @@
       <c r="C197" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D197" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Bulgaria.png</v>
+      </c>
+      <c r="E197" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Bulgaria.png</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A198" s="1" t="s">
         <v>201</v>
       </c>
@@ -3878,8 +5491,16 @@
       <c r="C198" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D198" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Burkina Faso.png</v>
+      </c>
+      <c r="E198" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Burkina_Faso.png</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A199" s="1" t="s">
         <v>202</v>
       </c>
@@ -3889,8 +5510,16 @@
       <c r="C199" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D199" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Burundi.png</v>
+      </c>
+      <c r="E199" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Burundi.png</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A200" s="1" t="s">
         <v>203</v>
       </c>
@@ -3900,8 +5529,16 @@
       <c r="C200" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D200" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Cambodia.png</v>
+      </c>
+      <c r="E200" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Cambodia.png</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A201" s="1" t="s">
         <v>204</v>
       </c>
@@ -3911,8 +5548,16 @@
       <c r="C201" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D201" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Cameroon.png</v>
+      </c>
+      <c r="E201" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Cameroon.png</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A202" s="1" t="s">
         <v>205</v>
       </c>
@@ -3922,8 +5567,16 @@
       <c r="C202" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D202" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Canada.png</v>
+      </c>
+      <c r="E202" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Canada.png</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A203" s="1" t="s">
         <v>206</v>
       </c>
@@ -3933,8 +5586,16 @@
       <c r="C203" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D203" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Cape Verde.png</v>
+      </c>
+      <c r="E203" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Cape_Verde.png</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A204" s="1" t="s">
         <v>207</v>
       </c>
@@ -3944,8 +5605,16 @@
       <c r="C204" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D204" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Central Africa.png</v>
+      </c>
+      <c r="E204" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Central_Africa.png</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A205" s="1" t="s">
         <v>208</v>
       </c>
@@ -3955,8 +5624,16 @@
       <c r="C205" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D205" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Chad.png</v>
+      </c>
+      <c r="E205" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Chad.png</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A206" s="1" t="s">
         <v>209</v>
       </c>
@@ -3966,8 +5643,16 @@
       <c r="C206" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D206" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Chile.png</v>
+      </c>
+      <c r="E206" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Chile.png</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A207" s="1" t="s">
         <v>210</v>
       </c>
@@ -3977,8 +5662,16 @@
       <c r="C207" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D207" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\China.png</v>
+      </c>
+      <c r="E207" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\China.png</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A208" s="1" t="s">
         <v>211</v>
       </c>
@@ -3988,8 +5681,16 @@
       <c r="C208" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D208" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Colombia.png</v>
+      </c>
+      <c r="E208" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Colombia.png</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A209" s="1" t="s">
         <v>212</v>
       </c>
@@ -3999,8 +5700,16 @@
       <c r="C209" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D209" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Comoros.png</v>
+      </c>
+      <c r="E209" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Comoros.png</v>
+      </c>
+    </row>
+    <row r="210" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A210" s="1" t="s">
         <v>213</v>
       </c>
@@ -4010,8 +5719,16 @@
       <c r="C210" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D210" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Congo DR.png</v>
+      </c>
+      <c r="E210" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Congo_DR.png</v>
+      </c>
+    </row>
+    <row r="211" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A211" s="1" t="s">
         <v>214</v>
       </c>
@@ -4021,8 +5738,16 @@
       <c r="C211" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D211" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Congo.png</v>
+      </c>
+      <c r="E211" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Congo.png</v>
+      </c>
+    </row>
+    <row r="212" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A212" s="1" t="s">
         <v>215</v>
       </c>
@@ -4032,8 +5757,16 @@
       <c r="C212" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D212" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Costa Rica.png</v>
+      </c>
+      <c r="E212" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Costa_Rica.png</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A213" s="1" t="s">
         <v>216</v>
       </c>
@@ -4043,8 +5776,16 @@
       <c r="C213" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D213" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Croatia.png</v>
+      </c>
+      <c r="E213" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Croatia.png</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A214" s="1" t="s">
         <v>217</v>
       </c>
@@ -4054,8 +5795,16 @@
       <c r="C214" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D214" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Cuba.png</v>
+      </c>
+      <c r="E214" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Cuba.png</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A215" s="1" t="s">
         <v>218</v>
       </c>
@@ -4065,8 +5814,16 @@
       <c r="C215" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D215" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Cyprus.png</v>
+      </c>
+      <c r="E215" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Cyprus.png</v>
+      </c>
+    </row>
+    <row r="216" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A216" s="1" t="s">
         <v>219</v>
       </c>
@@ -4076,8 +5833,16 @@
       <c r="C216" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D216" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Czech.png</v>
+      </c>
+      <c r="E216" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Czech.png</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A217" s="1" t="s">
         <v>220</v>
       </c>
@@ -4087,8 +5852,16 @@
       <c r="C217" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D217" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Denmark.png</v>
+      </c>
+      <c r="E217" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Denmark.png</v>
+      </c>
+    </row>
+    <row r="218" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A218" s="1" t="s">
         <v>221</v>
       </c>
@@ -4098,8 +5871,16 @@
       <c r="C218" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D218" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Djibouti.png</v>
+      </c>
+      <c r="E218" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Djibouti.png</v>
+      </c>
+    </row>
+    <row r="219" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A219" s="1" t="s">
         <v>222</v>
       </c>
@@ -4109,8 +5890,16 @@
       <c r="C219" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D219" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Dominica.png</v>
+      </c>
+      <c r="E219" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Dominica.png</v>
+      </c>
+    </row>
+    <row r="220" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A220" s="1" t="s">
         <v>223</v>
       </c>
@@ -4120,8 +5909,16 @@
       <c r="C220" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D220" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Dominican.png</v>
+      </c>
+      <c r="E220" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Dominican.png</v>
+      </c>
+    </row>
+    <row r="221" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A221" s="1" t="s">
         <v>224</v>
       </c>
@@ -4131,8 +5928,16 @@
       <c r="C221" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D221" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\East Timor.png</v>
+      </c>
+      <c r="E221" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\East_Timor.png</v>
+      </c>
+    </row>
+    <row r="222" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A222" s="1" t="s">
         <v>225</v>
       </c>
@@ -4142,8 +5947,16 @@
       <c r="C222" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D222" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Ecuador.png</v>
+      </c>
+      <c r="E222" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Ecuador.png</v>
+      </c>
+    </row>
+    <row r="223" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A223" s="1" t="s">
         <v>226</v>
       </c>
@@ -4153,8 +5966,16 @@
       <c r="C223" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D223" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Egypt.png</v>
+      </c>
+      <c r="E223" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Egypt.png</v>
+      </c>
+    </row>
+    <row r="224" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A224" s="1" t="s">
         <v>227</v>
       </c>
@@ -4164,8 +5985,16 @@
       <c r="C224" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D224" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\El Salvador.png</v>
+      </c>
+      <c r="E224" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\El_Salvador.png</v>
+      </c>
+    </row>
+    <row r="225" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A225" s="1" t="s">
         <v>228</v>
       </c>
@@ -4175,8 +6004,16 @@
       <c r="C225" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D225" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Eritrea.png</v>
+      </c>
+      <c r="E225" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Eritrea.png</v>
+      </c>
+    </row>
+    <row r="226" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A226" s="1" t="s">
         <v>229</v>
       </c>
@@ -4186,8 +6023,16 @@
       <c r="C226" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D226" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Estonia.png</v>
+      </c>
+      <c r="E226" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Estonia.png</v>
+      </c>
+    </row>
+    <row r="227" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A227" s="1" t="s">
         <v>230</v>
       </c>
@@ -4197,8 +6042,16 @@
       <c r="C227" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D227" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Eswatini.png</v>
+      </c>
+      <c r="E227" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Eswatini.png</v>
+      </c>
+    </row>
+    <row r="228" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A228" s="1" t="s">
         <v>231</v>
       </c>
@@ -4208,8 +6061,16 @@
       <c r="C228" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D228" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Ethiopia.png</v>
+      </c>
+      <c r="E228" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Ethiopia.png</v>
+      </c>
+    </row>
+    <row r="229" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A229" s="1" t="s">
         <v>232</v>
       </c>
@@ -4219,8 +6080,16 @@
       <c r="C229" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D229" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Fiji.png</v>
+      </c>
+      <c r="E229" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Fiji.png</v>
+      </c>
+    </row>
+    <row r="230" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A230" s="1" t="s">
         <v>233</v>
       </c>
@@ -4230,8 +6099,16 @@
       <c r="C230" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D230" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Finland.png</v>
+      </c>
+      <c r="E230" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Finland.png</v>
+      </c>
+    </row>
+    <row r="231" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A231" s="1" t="s">
         <v>234</v>
       </c>
@@ -4241,8 +6118,16 @@
       <c r="C231" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D231" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\France.png</v>
+      </c>
+      <c r="E231" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\France.png</v>
+      </c>
+    </row>
+    <row r="232" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A232" s="1" t="s">
         <v>235</v>
       </c>
@@ -4252,8 +6137,16 @@
       <c r="C232" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D232" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Gabon.png</v>
+      </c>
+      <c r="E232" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Gabon.png</v>
+      </c>
+    </row>
+    <row r="233" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A233" s="1" t="s">
         <v>236</v>
       </c>
@@ -4263,8 +6156,16 @@
       <c r="C233" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D233" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Gambia.png</v>
+      </c>
+      <c r="E233" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Gambia.png</v>
+      </c>
+    </row>
+    <row r="234" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A234" s="1" t="s">
         <v>237</v>
       </c>
@@ -4274,8 +6175,16 @@
       <c r="C234" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D234" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Georgia.png</v>
+      </c>
+      <c r="E234" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Georgia.png</v>
+      </c>
+    </row>
+    <row r="235" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A235" s="1" t="s">
         <v>238</v>
       </c>
@@ -4285,8 +6194,16 @@
       <c r="C235" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D235" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Germany.png</v>
+      </c>
+      <c r="E235" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Germany.png</v>
+      </c>
+    </row>
+    <row r="236" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A236" s="1" t="s">
         <v>239</v>
       </c>
@@ -4296,8 +6213,16 @@
       <c r="C236" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D236" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Ghana.png</v>
+      </c>
+      <c r="E236" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Ghana.png</v>
+      </c>
+    </row>
+    <row r="237" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A237" s="1" t="s">
         <v>240</v>
       </c>
@@ -4307,8 +6232,16 @@
       <c r="C237" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D237" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Greece.png</v>
+      </c>
+      <c r="E237" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Greece.png</v>
+      </c>
+    </row>
+    <row r="238" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A238" s="1" t="s">
         <v>241</v>
       </c>
@@ -4318,8 +6251,16 @@
       <c r="C238" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D238" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Grenada.png</v>
+      </c>
+      <c r="E238" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Grenada.png</v>
+      </c>
+    </row>
+    <row r="239" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A239" s="1" t="s">
         <v>63</v>
       </c>
@@ -4329,8 +6270,16 @@
       <c r="C239" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="240" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D239" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Guatemala.png</v>
+      </c>
+      <c r="E239" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Guatemala.png</v>
+      </c>
+    </row>
+    <row r="240" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A240" s="1" t="s">
         <v>242</v>
       </c>
@@ -4340,8 +6289,16 @@
       <c r="C240" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="241" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D240" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Guinea Bissau.png</v>
+      </c>
+      <c r="E240" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Guinea_Bissau.png</v>
+      </c>
+    </row>
+    <row r="241" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A241" s="1" t="s">
         <v>243</v>
       </c>
@@ -4351,8 +6308,16 @@
       <c r="C241" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="242" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D241" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Guinea.png</v>
+      </c>
+      <c r="E241" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Guinea.png</v>
+      </c>
+    </row>
+    <row r="242" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A242" s="1" t="s">
         <v>244</v>
       </c>
@@ -4362,8 +6327,16 @@
       <c r="C242" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="243" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D242" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Guyana.png</v>
+      </c>
+      <c r="E242" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Guyana.png</v>
+      </c>
+    </row>
+    <row r="243" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A243" s="1" t="s">
         <v>245</v>
       </c>
@@ -4373,8 +6346,16 @@
       <c r="C243" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="244" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D243" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Haiti.png</v>
+      </c>
+      <c r="E243" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Haiti.png</v>
+      </c>
+    </row>
+    <row r="244" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A244" s="1" t="s">
         <v>246</v>
       </c>
@@ -4384,8 +6365,16 @@
       <c r="C244" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="245" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D244" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Honduras.png</v>
+      </c>
+      <c r="E244" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Honduras.png</v>
+      </c>
+    </row>
+    <row r="245" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A245" s="1" t="s">
         <v>247</v>
       </c>
@@ -4395,8 +6384,16 @@
       <c r="C245" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="246" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D245" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Hungary.png</v>
+      </c>
+      <c r="E245" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Hungary.png</v>
+      </c>
+    </row>
+    <row r="246" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A246" s="1" t="s">
         <v>248</v>
       </c>
@@ -4406,8 +6403,16 @@
       <c r="C246" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="247" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D246" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Iceland.png</v>
+      </c>
+      <c r="E246" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Iceland.png</v>
+      </c>
+    </row>
+    <row r="247" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A247" s="1" t="s">
         <v>249</v>
       </c>
@@ -4417,8 +6422,16 @@
       <c r="C247" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="248" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D247" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\India.png</v>
+      </c>
+      <c r="E247" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\India.png</v>
+      </c>
+    </row>
+    <row r="248" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A248" s="1" t="s">
         <v>250</v>
       </c>
@@ -4428,8 +6441,16 @@
       <c r="C248" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="249" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D248" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Indonesia.png</v>
+      </c>
+      <c r="E248" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Indonesia.png</v>
+      </c>
+    </row>
+    <row r="249" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A249" s="1" t="s">
         <v>251</v>
       </c>
@@ -4439,8 +6460,16 @@
       <c r="C249" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="250" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D249" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Iran.png</v>
+      </c>
+      <c r="E249" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Iran.png</v>
+      </c>
+    </row>
+    <row r="250" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A250" s="1" t="s">
         <v>252</v>
       </c>
@@ -4450,8 +6479,16 @@
       <c r="C250" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="251" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D250" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Iraq.png</v>
+      </c>
+      <c r="E250" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Iraq.png</v>
+      </c>
+    </row>
+    <row r="251" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A251" s="1" t="s">
         <v>253</v>
       </c>
@@ -4461,8 +6498,16 @@
       <c r="C251" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="252" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D251" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Ireland.png</v>
+      </c>
+      <c r="E251" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Ireland.png</v>
+      </c>
+    </row>
+    <row r="252" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A252" s="1" t="s">
         <v>254</v>
       </c>
@@ -4472,8 +6517,16 @@
       <c r="C252" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="253" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D252" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Italy.png</v>
+      </c>
+      <c r="E252" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Italy.png</v>
+      </c>
+    </row>
+    <row r="253" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A253" s="1" t="s">
         <v>255</v>
       </c>
@@ -4483,8 +6536,16 @@
       <c r="C253" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="254" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D253" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Ivory Coast.png</v>
+      </c>
+      <c r="E253" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Ivory_Coast.png</v>
+      </c>
+    </row>
+    <row r="254" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A254" s="1" t="s">
         <v>256</v>
       </c>
@@ -4494,8 +6555,16 @@
       <c r="C254" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="255" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D254" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Jamaica.png</v>
+      </c>
+      <c r="E254" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Jamaica.png</v>
+      </c>
+    </row>
+    <row r="255" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A255" s="1" t="s">
         <v>257</v>
       </c>
@@ -4505,8 +6574,16 @@
       <c r="C255" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="256" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D255" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Japan.png</v>
+      </c>
+      <c r="E255" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Japan.png</v>
+      </c>
+    </row>
+    <row r="256" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A256" s="1" t="s">
         <v>258</v>
       </c>
@@ -4516,8 +6593,16 @@
       <c r="C256" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="257" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D256" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Jordan.png</v>
+      </c>
+      <c r="E256" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Jordan.png</v>
+      </c>
+    </row>
+    <row r="257" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A257" s="1" t="s">
         <v>259</v>
       </c>
@@ -4527,8 +6612,16 @@
       <c r="C257" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="258" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D257" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Kazakhstan.png</v>
+      </c>
+      <c r="E257" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Kazakhstan.png</v>
+      </c>
+    </row>
+    <row r="258" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A258" s="1" t="s">
         <v>260</v>
       </c>
@@ -4538,8 +6631,16 @@
       <c r="C258" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="259" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D258" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Kenya.png</v>
+      </c>
+      <c r="E258" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Kenya.png</v>
+      </c>
+    </row>
+    <row r="259" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A259" s="1" t="s">
         <v>261</v>
       </c>
@@ -4549,8 +6650,16 @@
       <c r="C259" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="260" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D259" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Kiribati.png</v>
+      </c>
+      <c r="E259" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Kiribati.png</v>
+      </c>
+    </row>
+    <row r="260" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A260" s="1" t="s">
         <v>79</v>
       </c>
@@ -4560,8 +6669,16 @@
       <c r="C260" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="261" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D260" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Kuwait.png</v>
+      </c>
+      <c r="E260" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Kuwait.png</v>
+      </c>
+    </row>
+    <row r="261" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A261" s="1" t="s">
         <v>262</v>
       </c>
@@ -4571,8 +6688,16 @@
       <c r="C261" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="262" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D261" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Kyrgyzstan.png</v>
+      </c>
+      <c r="E261" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Kyrgyzstan.png</v>
+      </c>
+    </row>
+    <row r="262" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A262" s="1" t="s">
         <v>263</v>
       </c>
@@ -4582,8 +6707,16 @@
       <c r="C262" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="263" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D262" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Laos.png</v>
+      </c>
+      <c r="E262" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Laos.png</v>
+      </c>
+    </row>
+    <row r="263" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A263" s="1" t="s">
         <v>264</v>
       </c>
@@ -4593,8 +6726,16 @@
       <c r="C263" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="264" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D263" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Latvia.png</v>
+      </c>
+      <c r="E263" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Latvia.png</v>
+      </c>
+    </row>
+    <row r="264" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A264" s="1" t="s">
         <v>265</v>
       </c>
@@ -4604,8 +6745,16 @@
       <c r="C264" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="265" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D264" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Lebanon.png</v>
+      </c>
+      <c r="E264" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Lebanon.png</v>
+      </c>
+    </row>
+    <row r="265" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A265" s="1" t="s">
         <v>266</v>
       </c>
@@ -4615,8 +6764,16 @@
       <c r="C265" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="266" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D265" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Lesotho.png</v>
+      </c>
+      <c r="E265" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Lesotho.png</v>
+      </c>
+    </row>
+    <row r="266" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A266" s="1" t="s">
         <v>267</v>
       </c>
@@ -4626,8 +6783,16 @@
       <c r="C266" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="267" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D266" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Liberia.png</v>
+      </c>
+      <c r="E266" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Liberia.png</v>
+      </c>
+    </row>
+    <row r="267" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A267" s="1" t="s">
         <v>268</v>
       </c>
@@ -4637,8 +6802,16 @@
       <c r="C267" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="268" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D267" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Libya.png</v>
+      </c>
+      <c r="E267" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Libya.png</v>
+      </c>
+    </row>
+    <row r="268" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A268" s="1" t="s">
         <v>269</v>
       </c>
@@ -4648,8 +6821,16 @@
       <c r="C268" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="269" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D268" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Liechtenstein.png</v>
+      </c>
+      <c r="E268" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Liechtenstein.png</v>
+      </c>
+    </row>
+    <row r="269" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A269" s="1" t="s">
         <v>270</v>
       </c>
@@ -4659,8 +6840,16 @@
       <c r="C269" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="270" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D269" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Lithuania.png</v>
+      </c>
+      <c r="E269" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Lithuania.png</v>
+      </c>
+    </row>
+    <row r="270" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A270" s="1" t="s">
         <v>90</v>
       </c>
@@ -4670,8 +6859,16 @@
       <c r="C270" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="271" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D270" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Luxembourg.png</v>
+      </c>
+      <c r="E270" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Luxembourg.png</v>
+      </c>
+    </row>
+    <row r="271" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A271" s="1" t="s">
         <v>271</v>
       </c>
@@ -4681,8 +6878,16 @@
       <c r="C271" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="272" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D271" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Macedonia.png</v>
+      </c>
+      <c r="E271" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Macedonia.png</v>
+      </c>
+    </row>
+    <row r="272" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A272" s="1" t="s">
         <v>272</v>
       </c>
@@ -4692,8 +6897,16 @@
       <c r="C272" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="273" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D272" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Madagascar.png</v>
+      </c>
+      <c r="E272" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Madagascar.png</v>
+      </c>
+    </row>
+    <row r="273" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A273" s="1" t="s">
         <v>273</v>
       </c>
@@ -4703,8 +6916,16 @@
       <c r="C273" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="274" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D273" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Malawi.png</v>
+      </c>
+      <c r="E273" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Malawi.png</v>
+      </c>
+    </row>
+    <row r="274" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A274" s="1" t="s">
         <v>274</v>
       </c>
@@ -4714,8 +6935,16 @@
       <c r="C274" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="275" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D274" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Malaysia.png</v>
+      </c>
+      <c r="E274" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Malaysia.png</v>
+      </c>
+    </row>
+    <row r="275" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A275" s="1" t="s">
         <v>275</v>
       </c>
@@ -4725,8 +6954,16 @@
       <c r="C275" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="276" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D275" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Maldives.png</v>
+      </c>
+      <c r="E275" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Maldives.png</v>
+      </c>
+    </row>
+    <row r="276" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A276" s="1" t="s">
         <v>276</v>
       </c>
@@ -4736,8 +6973,16 @@
       <c r="C276" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="277" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D276" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Mali.png</v>
+      </c>
+      <c r="E276" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Mali.png</v>
+      </c>
+    </row>
+    <row r="277" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A277" s="1" t="s">
         <v>277</v>
       </c>
@@ -4747,8 +6992,16 @@
       <c r="C277" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="278" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D277" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Malta.png</v>
+      </c>
+      <c r="E277" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Malta.png</v>
+      </c>
+    </row>
+    <row r="278" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A278" s="1" t="s">
         <v>278</v>
       </c>
@@ -4758,8 +7011,16 @@
       <c r="C278" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="279" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D278" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Mauritania.png</v>
+      </c>
+      <c r="E278" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Mauritania.png</v>
+      </c>
+    </row>
+    <row r="279" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A279" s="1" t="s">
         <v>279</v>
       </c>
@@ -4769,8 +7030,16 @@
       <c r="C279" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="280" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D279" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Mauritius.png</v>
+      </c>
+      <c r="E279" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Mauritius.png</v>
+      </c>
+    </row>
+    <row r="280" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A280" s="1" t="s">
         <v>280</v>
       </c>
@@ -4780,8 +7049,16 @@
       <c r="C280" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="281" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D280" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Mexico.png</v>
+      </c>
+      <c r="E280" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Mexico.png</v>
+      </c>
+    </row>
+    <row r="281" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A281" s="1" t="s">
         <v>281</v>
       </c>
@@ -4791,8 +7068,16 @@
       <c r="C281" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="282" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D281" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Moldova.png</v>
+      </c>
+      <c r="E281" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Moldova.png</v>
+      </c>
+    </row>
+    <row r="282" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A282" s="1" t="s">
         <v>102</v>
       </c>
@@ -4802,8 +7087,16 @@
       <c r="C282" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="283" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D282" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Monaco.png</v>
+      </c>
+      <c r="E282" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Monaco.png</v>
+      </c>
+    </row>
+    <row r="283" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A283" s="1" t="s">
         <v>282</v>
       </c>
@@ -4813,8 +7106,16 @@
       <c r="C283" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="284" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D283" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Mongolia.png</v>
+      </c>
+      <c r="E283" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Mongolia.png</v>
+      </c>
+    </row>
+    <row r="284" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A284" s="1" t="s">
         <v>283</v>
       </c>
@@ -4824,8 +7125,16 @@
       <c r="C284" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="285" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D284" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Montenegro.png</v>
+      </c>
+      <c r="E284" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Montenegro.png</v>
+      </c>
+    </row>
+    <row r="285" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A285" s="1" t="s">
         <v>284</v>
       </c>
@@ -4835,8 +7144,16 @@
       <c r="C285" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="286" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D285" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Morocco.png</v>
+      </c>
+      <c r="E285" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Morocco.png</v>
+      </c>
+    </row>
+    <row r="286" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A286" s="1" t="s">
         <v>285</v>
       </c>
@@ -4846,8 +7163,16 @@
       <c r="C286" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="287" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D286" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Mozambique.png</v>
+      </c>
+      <c r="E286" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Mozambique.png</v>
+      </c>
+    </row>
+    <row r="287" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A287" s="1" t="s">
         <v>286</v>
       </c>
@@ -4857,8 +7182,16 @@
       <c r="C287" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="288" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D287" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Myanmar.png</v>
+      </c>
+      <c r="E287" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Myanmar.png</v>
+      </c>
+    </row>
+    <row r="288" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A288" s="1" t="s">
         <v>287</v>
       </c>
@@ -4868,8 +7201,16 @@
       <c r="C288" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="289" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D288" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Namibia.png</v>
+      </c>
+      <c r="E288" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Namibia.png</v>
+      </c>
+    </row>
+    <row r="289" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A289" s="1" t="s">
         <v>288</v>
       </c>
@@ -4879,8 +7220,16 @@
       <c r="C289" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="290" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D289" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Nauru.png</v>
+      </c>
+      <c r="E289" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Nauru.png</v>
+      </c>
+    </row>
+    <row r="290" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A290" s="1" t="s">
         <v>289</v>
       </c>
@@ -4890,8 +7239,16 @@
       <c r="C290" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="291" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D290" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Nepal.png</v>
+      </c>
+      <c r="E290" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Nepal.png</v>
+      </c>
+    </row>
+    <row r="291" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A291" s="1" t="s">
         <v>290</v>
       </c>
@@ -4901,8 +7258,16 @@
       <c r="C291" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="292" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D291" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Netherlands.png</v>
+      </c>
+      <c r="E291" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Netherlands.png</v>
+      </c>
+    </row>
+    <row r="292" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A292" s="1" t="s">
         <v>291</v>
       </c>
@@ -4912,8 +7277,16 @@
       <c r="C292" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="293" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D292" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\New Zealand.png</v>
+      </c>
+      <c r="E292" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\New_Zealand.png</v>
+      </c>
+    </row>
+    <row r="293" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A293" s="1" t="s">
         <v>292</v>
       </c>
@@ -4923,8 +7296,16 @@
       <c r="C293" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="294" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D293" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Nicaragua.png</v>
+      </c>
+      <c r="E293" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Nicaragua.png</v>
+      </c>
+    </row>
+    <row r="294" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A294" s="1" t="s">
         <v>293</v>
       </c>
@@ -4934,8 +7315,16 @@
       <c r="C294" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="295" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D294" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Niger.png</v>
+      </c>
+      <c r="E294" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Niger.png</v>
+      </c>
+    </row>
+    <row r="295" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A295" s="1" t="s">
         <v>294</v>
       </c>
@@ -4945,8 +7334,16 @@
       <c r="C295" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="296" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D295" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Nigeria.png</v>
+      </c>
+      <c r="E295" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Nigeria.png</v>
+      </c>
+    </row>
+    <row r="296" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A296" s="1" t="s">
         <v>295</v>
       </c>
@@ -4956,8 +7353,16 @@
       <c r="C296" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="297" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D296" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\North Korea.png</v>
+      </c>
+      <c r="E296" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\North_Korea.png</v>
+      </c>
+    </row>
+    <row r="297" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A297" s="1" t="s">
         <v>296</v>
       </c>
@@ -4967,8 +7372,16 @@
       <c r="C297" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="298" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D297" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Norway.png</v>
+      </c>
+      <c r="E297" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Norway.png</v>
+      </c>
+    </row>
+    <row r="298" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A298" s="1" t="s">
         <v>297</v>
       </c>
@@ -4978,8 +7391,16 @@
       <c r="C298" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="299" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D298" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Oman.png</v>
+      </c>
+      <c r="E298" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Oman.png</v>
+      </c>
+    </row>
+    <row r="299" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A299" s="1" t="s">
         <v>298</v>
       </c>
@@ -4989,8 +7410,16 @@
       <c r="C299" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="300" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D299" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Pakistan.png</v>
+      </c>
+      <c r="E299" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Pakistan.png</v>
+      </c>
+    </row>
+    <row r="300" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A300" s="1" t="s">
         <v>299</v>
       </c>
@@ -5000,8 +7429,16 @@
       <c r="C300" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="301" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D300" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Palau.png</v>
+      </c>
+      <c r="E300" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Palau.png</v>
+      </c>
+    </row>
+    <row r="301" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A301" s="1" t="s">
         <v>300</v>
       </c>
@@ -5011,8 +7448,16 @@
       <c r="C301" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="302" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D301" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Palestine.png</v>
+      </c>
+      <c r="E301" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Palestine.png</v>
+      </c>
+    </row>
+    <row r="302" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A302" s="1" t="s">
         <v>301</v>
       </c>
@@ -5022,8 +7467,16 @@
       <c r="C302" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="303" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D302" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Panama.png</v>
+      </c>
+      <c r="E302" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Panama.png</v>
+      </c>
+    </row>
+    <row r="303" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A303" s="1" t="s">
         <v>302</v>
       </c>
@@ -5033,8 +7486,16 @@
       <c r="C303" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="304" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D303" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Papua New Guinea.png</v>
+      </c>
+      <c r="E303" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Papua_New_Guinea.png</v>
+      </c>
+    </row>
+    <row r="304" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A304" s="1" t="s">
         <v>303</v>
       </c>
@@ -5044,8 +7505,16 @@
       <c r="C304" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="305" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D304" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Paraguay.png</v>
+      </c>
+      <c r="E304" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Paraguay.png</v>
+      </c>
+    </row>
+    <row r="305" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A305" s="1" t="s">
         <v>304</v>
       </c>
@@ -5055,8 +7524,16 @@
       <c r="C305" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="306" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D305" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Peru.png</v>
+      </c>
+      <c r="E305" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Peru.png</v>
+      </c>
+    </row>
+    <row r="306" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A306" s="1" t="s">
         <v>305</v>
       </c>
@@ -5066,8 +7543,16 @@
       <c r="C306" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="307" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D306" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Philippines.png</v>
+      </c>
+      <c r="E306" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Philippines.png</v>
+      </c>
+    </row>
+    <row r="307" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A307" s="1" t="s">
         <v>306</v>
       </c>
@@ -5077,8 +7562,16 @@
       <c r="C307" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="308" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D307" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Poland.png</v>
+      </c>
+      <c r="E307" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Poland.png</v>
+      </c>
+    </row>
+    <row r="308" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A308" s="1" t="s">
         <v>307</v>
       </c>
@@ -5088,8 +7581,16 @@
       <c r="C308" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="309" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D308" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Portugal.png</v>
+      </c>
+      <c r="E308" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Portugal.png</v>
+      </c>
+    </row>
+    <row r="309" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A309" s="1" t="s">
         <v>308</v>
       </c>
@@ -5099,8 +7600,16 @@
       <c r="C309" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="310" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D309" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Qatar.png</v>
+      </c>
+      <c r="E309" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Qatar.png</v>
+      </c>
+    </row>
+    <row r="310" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A310" s="1" t="s">
         <v>309</v>
       </c>
@@ -5110,8 +7619,16 @@
       <c r="C310" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="311" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D310" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Romania.png</v>
+      </c>
+      <c r="E310" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Romania.png</v>
+      </c>
+    </row>
+    <row r="311" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A311" s="1" t="s">
         <v>310</v>
       </c>
@@ -5121,8 +7638,16 @@
       <c r="C311" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="312" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D311" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Russia.png</v>
+      </c>
+      <c r="E311" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Russia.png</v>
+      </c>
+    </row>
+    <row r="312" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A312" s="1" t="s">
         <v>311</v>
       </c>
@@ -5132,8 +7657,16 @@
       <c r="C312" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="313" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D312" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Rwanda.png</v>
+      </c>
+      <c r="E312" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Rwanda.png</v>
+      </c>
+    </row>
+    <row r="313" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A313" s="1" t="s">
         <v>312</v>
       </c>
@@ -5143,8 +7676,16 @@
       <c r="C313" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="314" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D313" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Saint Kitts.png</v>
+      </c>
+      <c r="E313" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Saint_Kitts.png</v>
+      </c>
+    </row>
+    <row r="314" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A314" s="1" t="s">
         <v>313</v>
       </c>
@@ -5154,8 +7695,16 @@
       <c r="C314" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="315" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D314" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Saint Lucia.png</v>
+      </c>
+      <c r="E314" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Saint_Lucia.png</v>
+      </c>
+    </row>
+    <row r="315" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A315" s="1" t="s">
         <v>314</v>
       </c>
@@ -5165,8 +7714,16 @@
       <c r="C315" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="316" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D315" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Saint Vincent.png</v>
+      </c>
+      <c r="E315" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Saint_Vincent.png</v>
+      </c>
+    </row>
+    <row r="316" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A316" s="1" t="s">
         <v>315</v>
       </c>
@@ -5176,8 +7733,16 @@
       <c r="C316" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="317" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D316" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Samoa.png</v>
+      </c>
+      <c r="E316" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Samoa.png</v>
+      </c>
+    </row>
+    <row r="317" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A317" s="1" t="s">
         <v>316</v>
       </c>
@@ -5187,8 +7752,16 @@
       <c r="C317" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="318" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D317" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\San Marino.png</v>
+      </c>
+      <c r="E317" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\San_Marino.png</v>
+      </c>
+    </row>
+    <row r="318" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A318" s="1" t="s">
         <v>317</v>
       </c>
@@ -5198,8 +7771,16 @@
       <c r="C318" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="319" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D318" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Sao Tome.png</v>
+      </c>
+      <c r="E318" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Sao_Tome.png</v>
+      </c>
+    </row>
+    <row r="319" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A319" s="1" t="s">
         <v>318</v>
       </c>
@@ -5209,8 +7790,16 @@
       <c r="C319" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="320" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D319" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Saudi Arabia.png</v>
+      </c>
+      <c r="E319" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Saudi_Arabia.png</v>
+      </c>
+    </row>
+    <row r="320" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A320" s="1" t="s">
         <v>319</v>
       </c>
@@ -5220,8 +7809,16 @@
       <c r="C320" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="321" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D320" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Senegal.png</v>
+      </c>
+      <c r="E320" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Senegal.png</v>
+      </c>
+    </row>
+    <row r="321" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A321" s="1" t="s">
         <v>320</v>
       </c>
@@ -5231,8 +7828,16 @@
       <c r="C321" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="322" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D321" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Serbia.png</v>
+      </c>
+      <c r="E321" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Serbia.png</v>
+      </c>
+    </row>
+    <row r="322" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A322" s="1" t="s">
         <v>321</v>
       </c>
@@ -5242,8 +7847,16 @@
       <c r="C322" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="323" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D322" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Seychelles.png</v>
+      </c>
+      <c r="E322" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Seychelles.png</v>
+      </c>
+    </row>
+    <row r="323" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A323" s="1" t="s">
         <v>322</v>
       </c>
@@ -5253,8 +7866,16 @@
       <c r="C323" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="324" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D323" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Sierra Leone.png</v>
+      </c>
+      <c r="E323" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Sierra_Leone.png</v>
+      </c>
+    </row>
+    <row r="324" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A324" s="1" t="s">
         <v>145</v>
       </c>
@@ -5264,8 +7885,16 @@
       <c r="C324" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="325" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D324" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Singapore.png</v>
+      </c>
+      <c r="E324" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Singapore.png</v>
+      </c>
+    </row>
+    <row r="325" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A325" s="1" t="s">
         <v>323</v>
       </c>
@@ -5275,8 +7904,16 @@
       <c r="C325" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="326" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D325" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Slovakia.png</v>
+      </c>
+      <c r="E325" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Slovakia.png</v>
+      </c>
+    </row>
+    <row r="326" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A326" s="1" t="s">
         <v>324</v>
       </c>
@@ -5286,8 +7923,16 @@
       <c r="C326" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="327" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D326" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Slovenia.png</v>
+      </c>
+      <c r="E326" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Slovenia.png</v>
+      </c>
+    </row>
+    <row r="327" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A327" s="1" t="s">
         <v>325</v>
       </c>
@@ -5297,8 +7942,16 @@
       <c r="C327" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="328" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D327" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Somalia.png</v>
+      </c>
+      <c r="E327" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Somalia.png</v>
+      </c>
+    </row>
+    <row r="328" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A328" s="1" t="s">
         <v>326</v>
       </c>
@@ -5308,8 +7961,16 @@
       <c r="C328" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="329" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D328" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\South Africa.png</v>
+      </c>
+      <c r="E328" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\South_Africa.png</v>
+      </c>
+    </row>
+    <row r="329" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A329" s="1" t="s">
         <v>327</v>
       </c>
@@ -5319,8 +7980,16 @@
       <c r="C329" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="330" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D329" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\South Korea.png</v>
+      </c>
+      <c r="E329" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\South_Korea.png</v>
+      </c>
+    </row>
+    <row r="330" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A330" s="1" t="s">
         <v>328</v>
       </c>
@@ -5330,8 +7999,16 @@
       <c r="C330" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="331" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D330" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\South Sudan.png</v>
+      </c>
+      <c r="E330" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\South_Sudan.png</v>
+      </c>
+    </row>
+    <row r="331" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A331" s="1" t="s">
         <v>329</v>
       </c>
@@ -5341,8 +8018,16 @@
       <c r="C331" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="332" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D331" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Spain.png</v>
+      </c>
+      <c r="E331" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Spain.png</v>
+      </c>
+    </row>
+    <row r="332" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A332" s="1" t="s">
         <v>330</v>
       </c>
@@ -5352,8 +8037,16 @@
       <c r="C332" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="333" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D332" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Sri Lanka.png</v>
+      </c>
+      <c r="E332" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Sri_Lanka.png</v>
+      </c>
+    </row>
+    <row r="333" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A333" s="1" t="s">
         <v>331</v>
       </c>
@@ -5363,8 +8056,16 @@
       <c r="C333" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="334" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D333" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Sudan.png</v>
+      </c>
+      <c r="E333" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Sudan.png</v>
+      </c>
+    </row>
+    <row r="334" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A334" s="1" t="s">
         <v>332</v>
       </c>
@@ -5374,8 +8075,16 @@
       <c r="C334" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="335" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D334" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Suriname.png</v>
+      </c>
+      <c r="E334" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Suriname.png</v>
+      </c>
+    </row>
+    <row r="335" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A335" s="1" t="s">
         <v>333</v>
       </c>
@@ -5385,8 +8094,16 @@
       <c r="C335" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="336" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D335" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Sweden.png</v>
+      </c>
+      <c r="E335" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Sweden.png</v>
+      </c>
+    </row>
+    <row r="336" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A336" s="1" t="s">
         <v>334</v>
       </c>
@@ -5396,8 +8113,16 @@
       <c r="C336" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="337" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D336" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Switzerland.png</v>
+      </c>
+      <c r="E336" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Switzerland.png</v>
+      </c>
+    </row>
+    <row r="337" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A337" s="1" t="s">
         <v>335</v>
       </c>
@@ -5407,8 +8132,16 @@
       <c r="C337" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="338" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D337" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Syria.png</v>
+      </c>
+      <c r="E337" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Syria.png</v>
+      </c>
+    </row>
+    <row r="338" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A338" s="1" t="s">
         <v>336</v>
       </c>
@@ -5418,8 +8151,16 @@
       <c r="C338" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="339" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D338" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Tajikistan.png</v>
+      </c>
+      <c r="E338" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Tajikistan.png</v>
+      </c>
+    </row>
+    <row r="339" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A339" s="1" t="s">
         <v>337</v>
       </c>
@@ -5429,8 +8170,16 @@
       <c r="C339" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="340" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D339" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Tanzania.png</v>
+      </c>
+      <c r="E339" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Tanzania.png</v>
+      </c>
+    </row>
+    <row r="340" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A340" s="1" t="s">
         <v>338</v>
       </c>
@@ -5440,8 +8189,16 @@
       <c r="C340" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="341" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D340" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Thailand.png</v>
+      </c>
+      <c r="E340" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Thailand.png</v>
+      </c>
+    </row>
+    <row r="341" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A341" s="1" t="s">
         <v>339</v>
       </c>
@@ -5451,8 +8208,16 @@
       <c r="C341" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="342" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D341" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Togo.png</v>
+      </c>
+      <c r="E341" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Togo.png</v>
+      </c>
+    </row>
+    <row r="342" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A342" s="1" t="s">
         <v>340</v>
       </c>
@@ -5462,8 +8227,16 @@
       <c r="C342" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="343" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D342" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Tonga.png</v>
+      </c>
+      <c r="E342" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Tonga.png</v>
+      </c>
+    </row>
+    <row r="343" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A343" s="1" t="s">
         <v>341</v>
       </c>
@@ -5473,8 +8246,16 @@
       <c r="C343" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="344" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D343" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Trinidad.png</v>
+      </c>
+      <c r="E343" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Trinidad.png</v>
+      </c>
+    </row>
+    <row r="344" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A344" s="1" t="s">
         <v>342</v>
       </c>
@@ -5484,8 +8265,16 @@
       <c r="C344" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="345" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D344" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Tunisia.png</v>
+      </c>
+      <c r="E344" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Tunisia.png</v>
+      </c>
+    </row>
+    <row r="345" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A345" s="1" t="s">
         <v>343</v>
       </c>
@@ -5495,8 +8284,16 @@
       <c r="C345" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="346" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D345" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Turkey.png</v>
+      </c>
+      <c r="E345" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Turkey.png</v>
+      </c>
+    </row>
+    <row r="346" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A346" s="1" t="s">
         <v>344</v>
       </c>
@@ -5506,8 +8303,16 @@
       <c r="C346" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="347" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D346" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Turkmenistan.png</v>
+      </c>
+      <c r="E346" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Turkmenistan.png</v>
+      </c>
+    </row>
+    <row r="347" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A347" s="1" t="s">
         <v>345</v>
       </c>
@@ -5517,8 +8322,16 @@
       <c r="C347" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="348" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D347" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Tuvalu.png</v>
+      </c>
+      <c r="E347" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Tuvalu.png</v>
+      </c>
+    </row>
+    <row r="348" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A348" s="1" t="s">
         <v>346</v>
       </c>
@@ -5528,8 +8341,16 @@
       <c r="C348" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="349" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D348" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Uganda.png</v>
+      </c>
+      <c r="E348" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Uganda.png</v>
+      </c>
+    </row>
+    <row r="349" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A349" s="1" t="s">
         <v>347</v>
       </c>
@@ -5539,8 +8360,16 @@
       <c r="C349" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="350" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D349" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Ukraine.png</v>
+      </c>
+      <c r="E349" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Ukraine.png</v>
+      </c>
+    </row>
+    <row r="350" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A350" s="1" t="s">
         <v>348</v>
       </c>
@@ -5550,8 +8379,16 @@
       <c r="C350" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="351" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D350" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\United Kingdom.png</v>
+      </c>
+      <c r="E350" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\United_Kingdom.png</v>
+      </c>
+    </row>
+    <row r="351" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A351" s="1" t="s">
         <v>349</v>
       </c>
@@ -5561,8 +8398,16 @@
       <c r="C351" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="352" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D351" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\United States.png</v>
+      </c>
+      <c r="E351" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\United_States.png</v>
+      </c>
+    </row>
+    <row r="352" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A352" s="1" t="s">
         <v>350</v>
       </c>
@@ -5572,8 +8417,16 @@
       <c r="C352" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="353" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D352" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Uruguay.png</v>
+      </c>
+      <c r="E352" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Uruguay.png</v>
+      </c>
+    </row>
+    <row r="353" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A353" s="1" t="s">
         <v>351</v>
       </c>
@@ -5583,8 +8436,16 @@
       <c r="C353" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="354" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D353" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Uzbekistan.png</v>
+      </c>
+      <c r="E353" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Uzbekistan.png</v>
+      </c>
+    </row>
+    <row r="354" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A354" s="1" t="s">
         <v>162</v>
       </c>
@@ -5594,8 +8455,16 @@
       <c r="C354" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="355" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D354" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Vatican.png</v>
+      </c>
+      <c r="E354" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Vatican.png</v>
+      </c>
+    </row>
+    <row r="355" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A355" s="1" t="s">
         <v>352</v>
       </c>
@@ -5605,8 +8474,16 @@
       <c r="C355" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="356" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D355" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Venezuela.png</v>
+      </c>
+      <c r="E355" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Venezuela.png</v>
+      </c>
+    </row>
+    <row r="356" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A356" s="1" t="s">
         <v>353</v>
       </c>
@@ -5616,8 +8493,16 @@
       <c r="C356" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="357" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D356" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Vietnam.png</v>
+      </c>
+      <c r="E356" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Vietnam.png</v>
+      </c>
+    </row>
+    <row r="357" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A357" s="1" t="s">
         <v>354</v>
       </c>
@@ -5627,8 +8512,16 @@
       <c r="C357" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="358" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D357" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Yemen.png</v>
+      </c>
+      <c r="E357" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Yemen.png</v>
+      </c>
+    </row>
+    <row r="358" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A358" s="1" t="s">
         <v>355</v>
       </c>
@@ -5638,8 +8531,16 @@
       <c r="C358" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="359" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D358" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Zambia.png</v>
+      </c>
+      <c r="E358" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Zambia.png</v>
+      </c>
+    </row>
+    <row r="359" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A359" s="1" t="s">
         <v>356</v>
       </c>
@@ -5649,8 +8550,16 @@
       <c r="C359" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="360" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D359" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Zimbabwe.png</v>
+      </c>
+      <c r="E359" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\countries\Zimbabwe.png</v>
+      </c>
+    </row>
+    <row r="360" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A360" s="1" t="s">
         <v>357</v>
       </c>
@@ -5660,8 +8569,16 @@
       <c r="C360" s="1" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="361" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D360" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Acropolis.png</v>
+      </c>
+      <c r="E360" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Acropolis.png</v>
+      </c>
+    </row>
+    <row r="361" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A361" s="1" t="s">
         <v>359</v>
       </c>
@@ -5671,8 +8588,16 @@
       <c r="C361" s="1" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="362" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D361" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Alexander Lighthouse.png</v>
+      </c>
+      <c r="E361" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Alexander_Lighthouse.png</v>
+      </c>
+    </row>
+    <row r="362" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A362" s="1" t="s">
         <v>360</v>
       </c>
@@ -5682,8 +8607,16 @@
       <c r="C362" s="1" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="363" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D362" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Algeria Mosque.png</v>
+      </c>
+      <c r="E362" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Algeria_Mosque.png</v>
+      </c>
+    </row>
+    <row r="363" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A363" s="1" t="s">
         <v>361</v>
       </c>
@@ -5693,8 +8626,16 @@
       <c r="C363" s="1" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="364" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D363" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Angkur Wat.png</v>
+      </c>
+      <c r="E363" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Angkur_Wat.png</v>
+      </c>
+    </row>
+    <row r="364" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A364" s="1" t="s">
         <v>362</v>
       </c>
@@ -5704,8 +8645,16 @@
       <c r="C364" s="1" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="365" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D364" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Atomium.jpg</v>
+      </c>
+      <c r="E364" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Atomium.jpg</v>
+      </c>
+    </row>
+    <row r="365" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A365" s="1" t="s">
         <v>364</v>
       </c>
@@ -5715,8 +8664,16 @@
       <c r="C365" s="1" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="366" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D365" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Babylon Garden.png</v>
+      </c>
+      <c r="E365" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Babylon_Garden.png</v>
+      </c>
+    </row>
+    <row r="366" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A366" s="1" t="s">
         <v>365</v>
       </c>
@@ -5726,8 +8683,16 @@
       <c r="C366" s="1" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="367" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D366" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Bagrawia.png</v>
+      </c>
+      <c r="E366" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Bagrawia.png</v>
+      </c>
+    </row>
+    <row r="367" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A367" s="1" t="s">
         <v>366</v>
       </c>
@@ -5737,8 +8702,16 @@
       <c r="C367" s="1" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="368" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D367" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Basil Church.png</v>
+      </c>
+      <c r="E367" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Basil_Church.png</v>
+      </c>
+    </row>
+    <row r="368" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A368" s="1" t="s">
         <v>367</v>
       </c>
@@ -5748,8 +8721,16 @@
       <c r="C368" s="1" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="369" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D368" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Berlin Wall.png</v>
+      </c>
+      <c r="E368" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Berlin_Wall.png</v>
+      </c>
+    </row>
+    <row r="369" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A369" s="1" t="s">
         <v>368</v>
       </c>
@@ -5759,8 +8740,16 @@
       <c r="C369" s="1" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="370" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D369" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Big Ben.png</v>
+      </c>
+      <c r="E369" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Big_Ben.png</v>
+      </c>
+    </row>
+    <row r="370" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A370" s="1" t="s">
         <v>369</v>
       </c>
@@ -5770,8 +8759,16 @@
       <c r="C370" s="1" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="371" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D370" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Blue Mosque.jpg</v>
+      </c>
+      <c r="E370" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Blue_Mosque.jpg</v>
+      </c>
+    </row>
+    <row r="371" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A371" s="1" t="s">
         <v>370</v>
       </c>
@@ -5781,8 +8778,16 @@
       <c r="C371" s="1" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="372" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D371" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Borobudur.jpg</v>
+      </c>
+      <c r="E371" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Borobudur.jpg</v>
+      </c>
+    </row>
+    <row r="372" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A372" s="1" t="s">
         <v>371</v>
       </c>
@@ -5792,8 +8797,16 @@
       <c r="C372" s="1" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="373" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D372" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Brandenburg.jpg</v>
+      </c>
+      <c r="E372" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Brandenburg.jpg</v>
+      </c>
+    </row>
+    <row r="373" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A373" s="1" t="s">
         <v>372</v>
       </c>
@@ -5803,8 +8816,16 @@
       <c r="C373" s="1" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="374" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D373" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Brooklyn.png</v>
+      </c>
+      <c r="E373" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Brooklyn.png</v>
+      </c>
+    </row>
+    <row r="374" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A374" s="1" t="s">
         <v>373</v>
       </c>
@@ -5814,8 +8835,16 @@
       <c r="C374" s="1" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="375" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D374" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Burj Al Arab.jpg</v>
+      </c>
+      <c r="E374" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Burj_Al_Arab.jpg</v>
+      </c>
+    </row>
+    <row r="375" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A375" s="1" t="s">
         <v>374</v>
       </c>
@@ -5825,8 +8854,16 @@
       <c r="C375" s="1" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="376" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D375" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Burj Khalifa.png</v>
+      </c>
+      <c r="E375" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Burj_Khalifa.png</v>
+      </c>
+    </row>
+    <row r="376" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A376" s="1" t="s">
         <v>375</v>
       </c>
@@ -5836,8 +8873,16 @@
       <c r="C376" s="1" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="377" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D376" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Cairo Tower.png</v>
+      </c>
+      <c r="E376" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Cairo_Tower.png</v>
+      </c>
+    </row>
+    <row r="377" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A377" s="1" t="s">
         <v>376</v>
       </c>
@@ -5847,8 +8892,16 @@
       <c r="C377" s="1" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="378" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D377" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Cappadocia.jpeg</v>
+      </c>
+      <c r="E377" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Cappadocia.jpeg</v>
+      </c>
+    </row>
+    <row r="378" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A378" s="1" t="s">
         <v>378</v>
       </c>
@@ -5858,8 +8911,16 @@
       <c r="C378" s="1" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="379" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D378" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Colosseum.png</v>
+      </c>
+      <c r="E378" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Colosseum.png</v>
+      </c>
+    </row>
+    <row r="379" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A379" s="1" t="s">
         <v>379</v>
       </c>
@@ -5869,8 +8930,16 @@
       <c r="C379" s="1" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="380" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D379" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Dome of Rock.jpg</v>
+      </c>
+      <c r="E379" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Dome_of_Rock.jpg</v>
+      </c>
+    </row>
+    <row r="380" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A380" s="1" t="s">
         <v>380</v>
       </c>
@@ -5880,8 +8949,16 @@
       <c r="C380" s="1" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="381" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D380" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Easter Island.jpg</v>
+      </c>
+      <c r="E380" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Easter_Island.jpg</v>
+      </c>
+    </row>
+    <row r="381" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A381" s="1" t="s">
         <v>381</v>
       </c>
@@ -5891,8 +8968,16 @@
       <c r="C381" s="1" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="382" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D381" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Edinburgh Castle.png</v>
+      </c>
+      <c r="E381" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Edinburgh_Castle.png</v>
+      </c>
+    </row>
+    <row r="382" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A382" s="1" t="s">
         <v>382</v>
       </c>
@@ -5902,8 +8987,16 @@
       <c r="C382" s="1" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="383" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D382" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Eiffel Tower.png</v>
+      </c>
+      <c r="E382" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Eiffel_Tower.png</v>
+      </c>
+    </row>
+    <row r="383" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A383" s="1" t="s">
         <v>383</v>
       </c>
@@ -5913,8 +9006,16 @@
       <c r="C383" s="1" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="384" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D383" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Faisal Mosque.jpg</v>
+      </c>
+      <c r="E383" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Faisal_Mosque.jpg</v>
+      </c>
+    </row>
+    <row r="384" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A384" s="1" t="s">
         <v>384</v>
       </c>
@@ -5924,8 +9025,16 @@
       <c r="C384" s="1" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="385" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D384" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Forbidden City.png</v>
+      </c>
+      <c r="E384" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Forbidden_City.png</v>
+      </c>
+    </row>
+    <row r="385" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A385" s="1" t="s">
         <v>385</v>
       </c>
@@ -5935,8 +9044,16 @@
       <c r="C385" s="1" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="386" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D385" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Gate arch.png</v>
+      </c>
+      <c r="E385" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Gate_arch.png</v>
+      </c>
+    </row>
+    <row r="386" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A386" s="1" t="s">
         <v>386</v>
       </c>
@@ -5946,8 +9063,16 @@
       <c r="C386" s="1" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="387" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D386" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Gate Bridge.png</v>
+      </c>
+      <c r="E386" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Gate_Bridge.png</v>
+      </c>
+    </row>
+    <row r="387" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A387" s="1" t="s">
         <v>387</v>
       </c>
@@ -5957,8 +9082,16 @@
       <c r="C387" s="1" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="388" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D387" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Gerkin.png</v>
+      </c>
+      <c r="E387" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Gerkin.png</v>
+      </c>
+    </row>
+    <row r="388" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A388" s="1" t="s">
         <v>388</v>
       </c>
@@ -5968,8 +9101,16 @@
       <c r="C388" s="1" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="389" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D388" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Giza Pyramids.png</v>
+      </c>
+      <c r="E388" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Giza_Pyramids.png</v>
+      </c>
+    </row>
+    <row r="389" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A389" s="1" t="s">
         <v>389</v>
       </c>
@@ -5979,8 +9120,16 @@
       <c r="C389" s="1" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="390" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D389" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Grand Canyon.jpg</v>
+      </c>
+      <c r="E389" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Grand_Canyon.jpg</v>
+      </c>
+    </row>
+    <row r="390" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A390" s="1" t="s">
         <v>390</v>
       </c>
@@ -5990,8 +9139,16 @@
       <c r="C390" s="1" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="391" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D390" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Great Wall.png</v>
+      </c>
+      <c r="E390" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Great_Wall.png</v>
+      </c>
+    </row>
+    <row r="391" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A391" s="1" t="s">
         <v>391</v>
       </c>
@@ -6001,8 +9158,16 @@
       <c r="C391" s="1" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="392" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D391" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Hagia Sophia.png</v>
+      </c>
+      <c r="E391" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Hagia_Sophia.png</v>
+      </c>
+    </row>
+    <row r="392" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A392" s="1" t="s">
         <v>392</v>
       </c>
@@ -6012,8 +9177,16 @@
       <c r="C392" s="1" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="393" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D392" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Independence.jpg</v>
+      </c>
+      <c r="E392" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Independence.jpg</v>
+      </c>
+    </row>
+    <row r="393" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A393" s="1" t="s">
         <v>393</v>
       </c>
@@ -6023,8 +9196,16 @@
       <c r="C393" s="1" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="394" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D393" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Kaaba.jpg</v>
+      </c>
+      <c r="E393" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Kaaba.jpg</v>
+      </c>
+    </row>
+    <row r="394" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A394" s="1" t="s">
         <v>394</v>
       </c>
@@ -6034,8 +9215,16 @@
       <c r="C394" s="1" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="395" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D394" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Kilimanjaro.png</v>
+      </c>
+      <c r="E394" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Kilimanjaro.png</v>
+      </c>
+    </row>
+    <row r="395" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A395" s="1" t="s">
         <v>395</v>
       </c>
@@ -6045,8 +9234,16 @@
       <c r="C395" s="1" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="396" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D395" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Kinderdick.jpg</v>
+      </c>
+      <c r="E395" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Kinderdick.jpg</v>
+      </c>
+    </row>
+    <row r="396" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A396" s="1" t="s">
         <v>396</v>
       </c>
@@ -6056,8 +9253,16 @@
       <c r="C396" s="1" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="397" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D396" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Kuwait Towers.png</v>
+      </c>
+      <c r="E396" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Kuwait_Towers.png</v>
+      </c>
+    </row>
+    <row r="397" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A397" s="1" t="s">
         <v>397</v>
       </c>
@@ -6067,8 +9272,16 @@
       <c r="C397" s="1" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="398" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D397" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Liberty Statue.png</v>
+      </c>
+      <c r="E397" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Liberty_Statue.png</v>
+      </c>
+    </row>
+    <row r="398" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A398" s="1" t="s">
         <v>398</v>
       </c>
@@ -6078,8 +9291,16 @@
       <c r="C398" s="1" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="399" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D398" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\London Eye.png</v>
+      </c>
+      <c r="E398" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\London_Eye.png</v>
+      </c>
+    </row>
+    <row r="399" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A399" s="1" t="s">
         <v>399</v>
       </c>
@@ -6089,8 +9310,16 @@
       <c r="C399" s="1" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="400" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D399" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\London Tower.png</v>
+      </c>
+      <c r="E399" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\London_Tower.png</v>
+      </c>
+    </row>
+    <row r="400" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A400" s="1" t="s">
         <v>400</v>
       </c>
@@ -6100,8 +9329,16 @@
       <c r="C400" s="1" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="401" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D400" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Lotus Temple.jpg</v>
+      </c>
+      <c r="E400" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Lotus_Temple.jpg</v>
+      </c>
+    </row>
+    <row r="401" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A401" s="1" t="s">
         <v>401</v>
       </c>
@@ -6111,8 +9348,16 @@
       <c r="C401" s="1" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="402" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D401" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Louvre.png</v>
+      </c>
+      <c r="E401" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Louvre.png</v>
+      </c>
+    </row>
+    <row r="402" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A402" s="1" t="s">
         <v>402</v>
       </c>
@@ -6122,8 +9367,16 @@
       <c r="C402" s="1" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="403" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D402" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Luxor Temple.png</v>
+      </c>
+      <c r="E402" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Luxor_Temple.png</v>
+      </c>
+    </row>
+    <row r="403" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A403" s="1" t="s">
         <v>403</v>
       </c>
@@ -6133,8 +9386,16 @@
       <c r="C403" s="1" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="404" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D403" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Machu Picchu.png</v>
+      </c>
+      <c r="E403" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Machu_Picchu.png</v>
+      </c>
+    </row>
+    <row r="404" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A404" s="1" t="s">
         <v>404</v>
       </c>
@@ -6144,8 +9405,16 @@
       <c r="C404" s="1" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="405" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D404" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Martyrs Shrine.png</v>
+      </c>
+      <c r="E404" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Martyrs_Shrine.png</v>
+      </c>
+    </row>
+    <row r="405" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A405" s="1" t="s">
         <v>405</v>
       </c>
@@ -6155,8 +9424,16 @@
       <c r="C405" s="1" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="406" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D405" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Mayan pyramids.png</v>
+      </c>
+      <c r="E405" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Mayan_pyramids.png</v>
+      </c>
+    </row>
+    <row r="406" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A406" s="1" t="s">
         <v>406</v>
       </c>
@@ -6166,8 +9443,16 @@
       <c r="C406" s="1" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="407" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D406" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Mini Europe.jpg</v>
+      </c>
+      <c r="E406" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Mini_Europe.jpg</v>
+      </c>
+    </row>
+    <row r="407" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A407" s="1" t="s">
         <v>407</v>
       </c>
@@ -6177,8 +9462,16 @@
       <c r="C407" s="1" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="408" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D407" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Mount Everest.png</v>
+      </c>
+      <c r="E407" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Mount_Everest.png</v>
+      </c>
+    </row>
+    <row r="408" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A408" s="1" t="s">
         <v>408</v>
       </c>
@@ -6188,8 +9481,16 @@
       <c r="C408" s="1" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="409" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D408" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Mount Fuji.png</v>
+      </c>
+      <c r="E408" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Mount_Fuji.png</v>
+      </c>
+    </row>
+    <row r="409" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A409" s="1" t="s">
         <v>409</v>
       </c>
@@ -6199,8 +9500,16 @@
       <c r="C409" s="1" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="410" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D409" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Mount Rainbow.jpg</v>
+      </c>
+      <c r="E409" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Mount_Rainbow.jpg</v>
+      </c>
+    </row>
+    <row r="410" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A410" s="1" t="s">
         <v>410</v>
       </c>
@@ -6210,8 +9519,16 @@
       <c r="C410" s="1" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="411" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D410" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Mount Rushmore.png</v>
+      </c>
+      <c r="E410" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Mount_Rushmore.png</v>
+      </c>
+    </row>
+    <row r="411" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A411" s="1" t="s">
         <v>411</v>
       </c>
@@ -6221,8 +9538,16 @@
       <c r="C411" s="1" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="412" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D411" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Niagara.png</v>
+      </c>
+      <c r="E411" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Niagara.png</v>
+      </c>
+    </row>
+    <row r="412" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A412" s="1" t="s">
         <v>412</v>
       </c>
@@ -6232,8 +9557,16 @@
       <c r="C412" s="1" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="413" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D412" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Pamukkale.jpg</v>
+      </c>
+      <c r="E412" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Pamukkale.jpg</v>
+      </c>
+    </row>
+    <row r="413" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A413" s="1" t="s">
         <v>413</v>
       </c>
@@ -6243,8 +9576,16 @@
       <c r="C413" s="1" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="414" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D413" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Petra.png</v>
+      </c>
+      <c r="E413" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Petra.png</v>
+      </c>
+    </row>
+    <row r="414" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A414" s="1" t="s">
         <v>414</v>
       </c>
@@ -6254,8 +9595,16 @@
       <c r="C414" s="1" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="415" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D414" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Petronas.jpg</v>
+      </c>
+      <c r="E414" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Petronas.jpg</v>
+      </c>
+    </row>
+    <row r="415" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A415" s="1" t="s">
         <v>415</v>
       </c>
@@ -6265,8 +9614,16 @@
       <c r="C415" s="1" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="416" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D415" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Pompey.png</v>
+      </c>
+      <c r="E415" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Pompey.png</v>
+      </c>
+    </row>
+    <row r="416" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A416" s="1" t="s">
         <v>416</v>
       </c>
@@ -6276,8 +9633,16 @@
       <c r="C416" s="1" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="417" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D416" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Prophet Mosque.jpg</v>
+      </c>
+      <c r="E416" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Prophet_Mosque.jpg</v>
+      </c>
+    </row>
+    <row r="417" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A417" s="1" t="s">
         <v>417</v>
       </c>
@@ -6287,8 +9652,16 @@
       <c r="C417" s="1" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="418" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D417" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Sagrada.png</v>
+      </c>
+      <c r="E417" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Sagrada.png</v>
+      </c>
+    </row>
+    <row r="418" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A418" s="1" t="s">
         <v>418</v>
       </c>
@@ -6298,8 +9671,16 @@
       <c r="C418" s="1" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="419" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D418" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Shard Building.png</v>
+      </c>
+      <c r="E418" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Shard_Building.png</v>
+      </c>
+    </row>
+    <row r="419" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A419" s="1" t="s">
         <v>419</v>
       </c>
@@ -6309,8 +9690,16 @@
       <c r="C419" s="1" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="420" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D419" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Space needle.png</v>
+      </c>
+      <c r="E419" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Space_needle.png</v>
+      </c>
+    </row>
+    <row r="420" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A420" s="1" t="s">
         <v>420</v>
       </c>
@@ -6320,8 +9709,16 @@
       <c r="C420" s="1" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="421" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D420" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Sphinx.png</v>
+      </c>
+      <c r="E420" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Sphinx.png</v>
+      </c>
+    </row>
+    <row r="421" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A421" s="1" t="s">
         <v>421</v>
       </c>
@@ -6331,8 +9728,16 @@
       <c r="C421" s="1" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="422" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D421" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Stonehenge.png</v>
+      </c>
+      <c r="E421" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Stonehenge.png</v>
+      </c>
+    </row>
+    <row r="422" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A422" s="1" t="s">
         <v>422</v>
       </c>
@@ -6342,8 +9747,16 @@
       <c r="C422" s="1" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="423" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D422" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Sydney Opera.png</v>
+      </c>
+      <c r="E422" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Sydney_Opera.png</v>
+      </c>
+    </row>
+    <row r="423" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A423" s="1" t="s">
         <v>423</v>
       </c>
@@ -6353,8 +9766,16 @@
       <c r="C423" s="1" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="424" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D423" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Taipei Tower.jpg</v>
+      </c>
+      <c r="E423" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Taipei_Tower.jpg</v>
+      </c>
+    </row>
+    <row r="424" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A424" s="1" t="s">
         <v>424</v>
       </c>
@@ -6364,8 +9785,16 @@
       <c r="C424" s="1" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="425" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D424" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Taj Mahal.png</v>
+      </c>
+      <c r="E424" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Taj_Mahal.png</v>
+      </c>
+    </row>
+    <row r="425" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A425" s="1" t="s">
         <v>425</v>
       </c>
@@ -6375,8 +9804,16 @@
       <c r="C425" s="1" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="426" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D425" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Taourirt.png</v>
+      </c>
+      <c r="E425" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Taourirt.png</v>
+      </c>
+    </row>
+    <row r="426" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A426" s="1" t="s">
         <v>426</v>
       </c>
@@ -6386,8 +9823,16 @@
       <c r="C426" s="1" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="427" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D426" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Terracotta.jpg</v>
+      </c>
+      <c r="E426" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Terracotta.jpg</v>
+      </c>
+    </row>
+    <row r="427" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A427" s="1" t="s">
         <v>427</v>
       </c>
@@ -6397,8 +9842,16 @@
       <c r="C427" s="1" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="428" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D427" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\The City Hall.jpg</v>
+      </c>
+      <c r="E427" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\The_City_Hall.jpg</v>
+      </c>
+    </row>
+    <row r="428" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A428" s="1" t="s">
         <v>428</v>
       </c>
@@ -6408,8 +9861,16 @@
       <c r="C428" s="1" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="429" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D428" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\The Redeemer.png</v>
+      </c>
+      <c r="E428" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\The_Redeemer.png</v>
+      </c>
+    </row>
+    <row r="429" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A429" s="1" t="s">
         <v>429</v>
       </c>
@@ -6419,8 +9880,16 @@
       <c r="C429" s="1" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="430" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D429" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Tokyo Tower.png</v>
+      </c>
+      <c r="E429" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Tokyo_Tower.png</v>
+      </c>
+    </row>
+    <row r="430" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A430" s="1" t="s">
         <v>430</v>
       </c>
@@ -6430,8 +9899,16 @@
       <c r="C430" s="1" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="431" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D430" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Tower of Pisa.png</v>
+      </c>
+      <c r="E430" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Tower_of_Pisa.png</v>
+      </c>
+    </row>
+    <row r="431" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A431" s="1" t="s">
         <v>431</v>
       </c>
@@ -6441,8 +9918,16 @@
       <c r="C431" s="1" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="432" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D431" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Tripoli Tower.png</v>
+      </c>
+      <c r="E431" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Tripoli_Tower.png</v>
+      </c>
+    </row>
+    <row r="432" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A432" s="1" t="s">
         <v>432</v>
       </c>
@@ -6452,8 +9937,16 @@
       <c r="C432" s="1" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="433" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D432" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Umayyad Mosque.png</v>
+      </c>
+      <c r="E432" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Umayyad_Mosque.png</v>
+      </c>
+    </row>
+    <row r="433" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A433" s="1" t="s">
         <v>433</v>
       </c>
@@ -6463,8 +9956,16 @@
       <c r="C433" s="1" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="434" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D433" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Victoria Falls.png</v>
+      </c>
+      <c r="E433" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Victoria_Falls.png</v>
+      </c>
+    </row>
+    <row r="434" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A434" s="1" t="s">
         <v>434</v>
       </c>
@@ -6473,6 +9974,14 @@
       </c>
       <c r="C434" s="1" t="s">
         <v>358</v>
+      </c>
+      <c r="D434" s="2" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;images[[#This Row],[Name]]</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Zaytuna Mosque.png</v>
+      </c>
+      <c r="E434" s="1" t="str">
+        <f>images[[#This Row],[Folder Path]]&amp;SUBSTITUTE(images[[#This Row],[Name]]," ","_")</f>
+        <v>D:\0.GitHub\TriviaApps\GeoApp\GeoData\images\landmarks\Zaytuna_Mosque.png</v>
       </c>
     </row>
   </sheetData>
